--- a/Excel/7_RiceCultivation_WIP_v02.xlsx
+++ b/Excel/7_RiceCultivation_WIP_v02.xlsx
@@ -441,9 +441,9 @@
   <si>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.34998626667073579"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t xml:space="preserve">← </t>
@@ -451,9 +451,9 @@
     <r>
       <rPr>
         <i/>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.34998626667073579"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t>Automatically calculated, 12 months after start date</t>
@@ -582,9 +582,9 @@
   <si>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.34998626667073579"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t xml:space="preserve">← </t>
@@ -592,9 +592,9 @@
     <r>
       <rPr>
         <i/>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.34998626667073579"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t>DD/MM/YYYY or DD Month YYYY</t>
@@ -637,9 +637,9 @@
     <r>
       <rPr>
         <vertAlign val="subscript"/>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.24994659260841701"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t>CO2e</t>
@@ -734,9 +734,9 @@
       <rPr>
         <b/>
         <vertAlign val="subscript"/>
-        <sz val="16"/>
+        <sz val="14"/>
         <color theme="1" tint="0.24994659260841701"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t>N2O</t>
@@ -963,9 +963,9 @@
       <rPr>
         <b/>
         <vertAlign val="subscript"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color rgb="FF183C1B"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t>rice,wpo</t>
@@ -982,9 +982,9 @@
       <rPr>
         <b/>
         <vertAlign val="subscript"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color rgb="FF533001"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t>rice,wpo</t>
@@ -1013,9 +1013,9 @@
       <rPr>
         <b/>
         <vertAlign val="subscript"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color rgb="FF533001"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t>rice,wpo</t>
@@ -1191,115 +1191,113 @@
   </numFmts>
   <fonts count="64" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <i/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.14999847407452621"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.14999847407452621"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="20"/>
+      <sz val="18"/>
       <color rgb="FF183C1B"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF183C1B"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="12"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1" tint="0.14996795556505021"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <sz val="10"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
+      <family val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="20"/>
-      <color rgb="FFCC6600"/>
-      <name val="Times New Roman"/>
+      <sz val="10"/>
+      <color theme="1" tint="0.14996795556505021"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
-      <sz val="12"/>
+      <sz val="9"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color rgb="FFCC6600"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FFCC6600"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF533001"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
       <strike/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
       <i/>
       <strike/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
@@ -1310,314 +1308,308 @@
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="14"/>
       <color theme="0"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="10"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1" tint="0.249977111117893"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF008000"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FFCC6600"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="0"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1" tint="0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1" tint="0.249977111117893"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1" tint="0.249977111117893"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1" tint="0.249977111117893"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1" tint="0.249977111117893"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1" tint="0.249977111117893"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1" tint="0.249977111117893"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF242424"/>
       <name val="Consolas"/>
       <family val="3"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="0" tint="-4.9989318521683403E-2"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1" tint="0.14996795556505021"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1" tint="0.24994659260841701"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1" tint="0.24994659260841701"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
+      <color rgb="FFC44340"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="10"/>
+      <color rgb="FF008000"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color theme="1" tint="0.14996795556505021"/>
-      <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
+      <color rgb="FF0070C0"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="10"/>
+      <color rgb="FF0070C0"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
       <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1" tint="0.24994659260841701"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="14"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <vertAlign val="subscript"/>
+      <sz val="10"/>
+      <color theme="1" tint="0.24994659260841701"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FFC44340"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF008000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF0070C0"/>
-      <name val="Times New Roman"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color rgb="FF0070C0"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="0" tint="-0.499984740745262"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <sz val="10"/>
-      <color theme="0" tint="-0.499984740745262"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="16"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <vertAlign val="subscript"/>
-      <sz val="12"/>
-      <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
       <color rgb="FFCC6600"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
       <vertAlign val="subscript"/>
-      <sz val="16"/>
+      <sz val="14"/>
       <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color rgb="FFCC6600"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
-      <sz val="10"/>
+      <sz val="9"/>
       <color theme="6" tint="-0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
-      <sz val="10"/>
+      <sz val="9"/>
       <color theme="5" tint="-0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <u/>
-      <sz val="10"/>
+      <sz val="9"/>
       <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
-      <sz val="10"/>
+      <sz val="9"/>
       <color theme="1" tint="0.14999847407452621"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="20"/>
+      <sz val="18"/>
       <color theme="3" tint="9.9978637043366805E-2"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
       <vertAlign val="subscript"/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF183C1B"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
       <vertAlign val="subscript"/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF533001"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF404040"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
   </fonts>
@@ -2665,11 +2657,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2689,11 +2680,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2713,11 +2703,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2737,11 +2726,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2761,11 +2749,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2785,11 +2772,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2809,11 +2795,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2833,11 +2818,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2857,11 +2841,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2881,11 +2864,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2905,11 +2887,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2929,11 +2910,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2953,11 +2933,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2977,11 +2956,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3001,11 +2979,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3025,11 +3002,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3049,11 +3025,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3073,11 +3048,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3097,11 +3071,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3121,11 +3094,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3145,11 +3117,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3169,11 +3140,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3193,11 +3163,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3217,11 +3186,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3241,11 +3209,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3265,11 +3232,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3289,11 +3255,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3313,11 +3278,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3337,11 +3301,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3361,11 +3324,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3385,11 +3347,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3409,11 +3370,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3433,11 +3393,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3457,11 +3416,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3481,11 +3439,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3505,11 +3462,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3529,11 +3485,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3553,11 +3508,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3577,11 +3531,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3601,11 +3554,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3625,11 +3577,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3649,11 +3600,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3673,11 +3623,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3958,7 +3907,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -4679,17 +4628,17 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:fld id="{B4871EB4-5DC2-4D10-A8B6-A0CA4AE96D38}" type="TxLink">
-            <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
             <a:t>7.1.1-2 Rice cultivation CH4 emissions</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="1400" b="0">
+          <a:endParaRPr lang="en-AU" sz="1200" b="0">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -4761,17 +4710,17 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:fld id="{BE27ECB6-7EB0-4FD1-96B7-4F3159D16F11}" type="TxLink">
-            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
             <a:t>Emission factor for rice cultivation</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="1000">
+          <a:endParaRPr lang="en-AU" sz="900">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -4843,17 +4792,17 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:fld id="{6B50A416-30BE-4EDC-B99C-EA936883A985}" type="TxLink">
-            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="900" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
             <a:t>Methane emissions from rice cultivation</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="1000" b="1">
+          <a:endParaRPr lang="en-AU" sz="900" b="1">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -4981,17 +4930,17 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:fld id="{04DABD53-0B14-4646-BF1E-ABDF085372F8}" type="TxLink">
-            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
             <a:t>Organic amendments scaling factor</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="1000">
+          <a:endParaRPr lang="en-AU" sz="900">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -5163,14 +5112,14 @@
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:sSubPr>
                       <m:e>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝐸</m:t>
@@ -5178,13 +5127,13 @@
                       </m:e>
                       <m:sub>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝐶𝐻</m:t>
                         </m:r>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>4</m:t>
@@ -5192,7 +5141,7 @@
                       </m:sub>
                     </m:sSub>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
                       <m:t>=</m:t>
@@ -5202,14 +5151,14 @@
                         <m:chr m:val="∑"/>
                         <m:supHide m:val="on"/>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:naryPr>
                       <m:sub>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝑗</m:t>
@@ -5222,14 +5171,14 @@
                             <m:chr m:val="∑"/>
                             <m:supHide m:val="on"/>
                             <m:ctrlPr>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                             </m:ctrlPr>
                           </m:naryPr>
                           <m:sub>
                             <m:r>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                               <m:t>𝑘</m:t>
@@ -5242,14 +5191,14 @@
                                 <m:chr m:val="∑"/>
                                 <m:supHide m:val="on"/>
                                 <m:ctrlPr>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                 </m:ctrlPr>
                               </m:naryPr>
                               <m:sub>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝑚</m:t>
@@ -5262,14 +5211,14 @@
                                     <m:chr m:val="∑"/>
                                     <m:supHide m:val="on"/>
                                     <m:ctrlPr>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                     </m:ctrlPr>
                                   </m:naryPr>
                                   <m:sub>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝑇</m:t>
@@ -5280,7 +5229,7 @@
                                     <m:d>
                                       <m:dPr>
                                         <m:ctrlPr>
-                                          <a:rPr lang="en-AU" sz="1100" i="1">
+                                          <a:rPr lang="en-AU" sz="1000" i="1">
                                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                           </a:rPr>
                                         </m:ctrlPr>
@@ -5289,14 +5238,14 @@
                                         <m:sSub>
                                           <m:sSubPr>
                                             <m:ctrlPr>
-                                              <a:rPr lang="en-AU" sz="1100" i="1">
+                                              <a:rPr lang="en-AU" sz="1000" i="1">
                                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                               </a:rPr>
                                             </m:ctrlPr>
                                           </m:sSubPr>
                                           <m:e>
                                             <m:r>
-                                              <a:rPr lang="en-AU" sz="1100" i="1">
+                                              <a:rPr lang="en-AU" sz="1000" i="1">
                                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                               </a:rPr>
                                               <m:t>𝐷</m:t>
@@ -5304,7 +5253,7 @@
                                           </m:e>
                                           <m:sub>
                                             <m:r>
-                                              <a:rPr lang="en-AU" sz="1100" i="1">
+                                              <a:rPr lang="en-AU" sz="1000" i="1">
                                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                               </a:rPr>
                                               <m:t>𝑗𝑘</m:t>
@@ -5312,7 +5261,7 @@
                                           </m:sub>
                                         </m:sSub>
                                         <m:r>
-                                          <a:rPr lang="en-AU" sz="1100" i="1">
+                                          <a:rPr lang="en-AU" sz="1000" i="1">
                                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                           </a:rPr>
                                           <m:t>×</m:t>
@@ -5320,14 +5269,14 @@
                                         <m:sSub>
                                           <m:sSubPr>
                                             <m:ctrlPr>
-                                              <a:rPr lang="en-AU" sz="1100" i="1">
+                                              <a:rPr lang="en-AU" sz="1000" i="1">
                                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                               </a:rPr>
                                             </m:ctrlPr>
                                           </m:sSubPr>
                                           <m:e>
                                             <m:r>
-                                              <a:rPr lang="en-AU" sz="1100" i="1">
+                                              <a:rPr lang="en-AU" sz="1000" i="1">
                                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                               </a:rPr>
                                               <m:t>𝑀</m:t>
@@ -5335,7 +5284,7 @@
                                           </m:e>
                                           <m:sub>
                                             <m:r>
-                                              <a:rPr lang="en-AU" sz="1100" i="1">
+                                              <a:rPr lang="en-AU" sz="1000" i="1">
                                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                               </a:rPr>
                                               <m:t>𝑗𝑘𝑚𝑇</m:t>
@@ -5343,7 +5292,7 @@
                                           </m:sub>
                                         </m:sSub>
                                         <m:r>
-                                          <a:rPr lang="en-AU" sz="1100" i="1">
+                                          <a:rPr lang="en-AU" sz="1000" i="1">
                                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                           </a:rPr>
                                           <m:t>×</m:t>
@@ -5351,14 +5300,14 @@
                                         <m:sSub>
                                           <m:sSubPr>
                                             <m:ctrlPr>
-                                              <a:rPr lang="en-AU" sz="1100" i="1">
+                                              <a:rPr lang="en-AU" sz="1000" i="1">
                                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                               </a:rPr>
                                             </m:ctrlPr>
                                           </m:sSubPr>
                                           <m:e>
                                             <m:r>
-                                              <a:rPr lang="en-AU" sz="1100" i="1">
+                                              <a:rPr lang="en-AU" sz="1000" i="1">
                                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                               </a:rPr>
                                               <m:t>𝑁</m:t>
@@ -5366,7 +5315,7 @@
                                           </m:e>
                                           <m:sub>
                                             <m:r>
-                                              <a:rPr lang="en-AU" sz="1100" i="1">
+                                              <a:rPr lang="en-AU" sz="1000" i="1">
                                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                               </a:rPr>
                                               <m:t>𝑗𝑘</m:t>
@@ -5384,7 +5333,7 @@
                       </m:e>
                     </m:nary>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
                       <m:t>×</m:t>
@@ -5392,14 +5341,14 @@
                     <m:sSup>
                       <m:sSupPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:sSupPr>
                       <m:e>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>10</m:t>
@@ -5407,7 +5356,7 @@
                       </m:e>
                       <m:sup>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>−3</m:t>
@@ -5417,7 +5366,7 @@
                   </m:oMath>
                 </m:oMathPara>
               </a14:m>
-              <a:endParaRPr lang="en-AU" sz="1100"/>
+              <a:endParaRPr lang="en-AU" sz="1000"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -5465,12 +5414,12 @@
             <a:lstStyle/>
             <a:p>
               <a:r>
-                <a:rPr lang="en-AU" sz="1100" i="0">
+                <a:rPr lang="en-AU" sz="1000" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
                 <a:t>𝐸_𝐶𝐻4=∑8_𝑗▒∑8_𝑘▒∑8_𝑚▒∑8_𝑇▒(𝐷_𝑗𝑘×𝑀_𝑗𝑘𝑚𝑇×𝑁_𝑗𝑘 ) ×10^(−3)</a:t>
               </a:r>
-              <a:endParaRPr lang="en-AU" sz="1100"/>
+              <a:endParaRPr lang="en-AU" sz="1000"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -5534,7 +5483,7 @@
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMath>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" b="1" i="1">
+                      <a:rPr lang="en-AU" sz="1000" b="1" i="1">
                         <a:solidFill>
                           <a:srgbClr val="C00000"/>
                         </a:solidFill>
@@ -5543,7 +5492,7 @@
                       <m:t>𝑶𝑹𝑰𝑮𝑰𝑵𝑨𝑳</m:t>
                     </m:r>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" b="1" i="1">
+                      <a:rPr lang="en-AU" sz="1000" b="1" i="1">
                         <a:solidFill>
                           <a:srgbClr val="C00000"/>
                         </a:solidFill>
@@ -5552,7 +5501,7 @@
                       <m:t>: </m:t>
                     </m:r>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
                       <m:t>𝑆</m:t>
@@ -5560,14 +5509,14 @@
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:sSubPr>
                       <m:e>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝐹</m:t>
@@ -5575,7 +5524,7 @@
                       </m:e>
                       <m:sub>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝑜</m:t>
@@ -5583,7 +5532,7 @@
                       </m:sub>
                     </m:sSub>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
                       <m:t>=</m:t>
@@ -5591,7 +5540,7 @@
                     <m:sSup>
                       <m:sSupPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
@@ -5600,14 +5549,14 @@
                         <m:d>
                           <m:dPr>
                             <m:ctrlPr>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                             </m:ctrlPr>
                           </m:dPr>
                           <m:e>
                             <m:r>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                               <m:t>1+</m:t>
@@ -5617,14 +5566,14 @@
                                 <m:chr m:val="∑"/>
                                 <m:supHide m:val="on"/>
                                 <m:ctrlPr>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                 </m:ctrlPr>
                               </m:naryPr>
                               <m:sub>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝑜</m:t>
@@ -5633,7 +5582,7 @@
                               <m:sup/>
                               <m:e>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝑅𝑂</m:t>
@@ -5641,14 +5590,14 @@
                                 <m:sSub>
                                   <m:sSubPr>
                                     <m:ctrlPr>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                     </m:ctrlPr>
                                   </m:sSubPr>
                                   <m:e>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝐴</m:t>
@@ -5656,7 +5605,7 @@
                                   </m:e>
                                   <m:sub>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝑜</m:t>
@@ -5666,13 +5615,13 @@
                               </m:e>
                             </m:nary>
                             <m:r>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                               <m:t>×</m:t>
                             </m:r>
                             <m:r>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                               <m:t>𝐶𝐹𝑂</m:t>
@@ -5680,14 +5629,14 @@
                             <m:sSub>
                               <m:sSubPr>
                                 <m:ctrlPr>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                 </m:ctrlPr>
                               </m:sSubPr>
                               <m:e>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝐴</m:t>
@@ -5695,7 +5644,7 @@
                               </m:e>
                               <m:sub>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝑜</m:t>
@@ -5707,7 +5656,7 @@
                       </m:e>
                       <m:sup>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>0.59</m:t>
@@ -5717,7 +5666,7 @@
                   </m:oMath>
                 </m:oMathPara>
               </a14:m>
-              <a:endParaRPr lang="en-AU" sz="1100"/>
+              <a:endParaRPr lang="en-AU" sz="1000"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -5766,7 +5715,7 @@
             <a:p>
               <a:pPr/>
               <a:r>
-                <a:rPr lang="en-AU" sz="1100" b="1" i="0">
+                <a:rPr lang="en-AU" sz="1000" b="1" i="0">
                   <a:solidFill>
                     <a:srgbClr val="C00000"/>
                   </a:solidFill>
@@ -5775,12 +5724,12 @@
                 <a:t>𝑶𝑹𝑰𝑮𝑰𝑵𝑨𝑳: </a:t>
               </a:r>
               <a:r>
-                <a:rPr lang="en-AU" sz="1100" i="0">
+                <a:rPr lang="en-AU" sz="1000" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
                 <a:t>𝑆𝐹_𝑜=(1+∑8_𝑜▒〖𝑅𝑂𝐴_𝑜 〗×𝐶𝐹𝑂𝐴_𝑜 )^0.59</a:t>
               </a:r>
-              <a:endParaRPr lang="en-AU" sz="1100"/>
+              <a:endParaRPr lang="en-AU" sz="1000"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -5844,7 +5793,7 @@
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMath>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
                       <m:t>𝐸</m:t>
@@ -5852,14 +5801,14 @@
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:sSubPr>
                       <m:e>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝐹</m:t>
@@ -5867,19 +5816,19 @@
                       </m:e>
                       <m:sub>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝑟𝑖𝑐𝑒</m:t>
                         </m:r>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>,</m:t>
                         </m:r>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝑤𝑝𝑜</m:t>
@@ -5887,13 +5836,13 @@
                       </m:sub>
                     </m:sSub>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
                       <m:t>=</m:t>
                     </m:r>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
                       <m:t>𝐸</m:t>
@@ -5901,14 +5850,14 @@
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:sSubPr>
                       <m:e>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝐹</m:t>
@@ -5916,7 +5865,7 @@
                       </m:e>
                       <m:sub>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝑐</m:t>
@@ -5924,13 +5873,13 @@
                       </m:sub>
                     </m:sSub>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
                       <m:t>×</m:t>
                     </m:r>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
                       <m:t>𝑆</m:t>
@@ -5938,14 +5887,14 @@
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:sSubPr>
                       <m:e>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝐹</m:t>
@@ -5953,7 +5902,7 @@
                       </m:e>
                       <m:sub>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝑤</m:t>
@@ -5961,13 +5910,13 @@
                       </m:sub>
                     </m:sSub>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
                       <m:t>×</m:t>
                     </m:r>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
                       <m:t>𝑆</m:t>
@@ -5975,14 +5924,14 @@
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:sSubPr>
                       <m:e>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝐹</m:t>
@@ -5990,7 +5939,7 @@
                       </m:e>
                       <m:sub>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝑝</m:t>
@@ -5998,13 +5947,13 @@
                       </m:sub>
                     </m:sSub>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
                       <m:t>×</m:t>
                     </m:r>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
                       <m:t>𝑆</m:t>
@@ -6012,14 +5961,14 @@
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:sSubPr>
                       <m:e>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝐹</m:t>
@@ -6027,7 +5976,7 @@
                       </m:e>
                       <m:sub>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝑜</m:t>
@@ -6037,7 +5986,7 @@
                   </m:oMath>
                 </m:oMathPara>
               </a14:m>
-              <a:endParaRPr lang="en-AU" sz="1100"/>
+              <a:endParaRPr lang="en-AU" sz="1000"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -6085,12 +6034,12 @@
             <a:lstStyle/>
             <a:p>
               <a:r>
-                <a:rPr lang="en-AU" sz="1100" i="0">
+                <a:rPr lang="en-AU" sz="1000" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
                 <a:t>𝐸𝐹_(𝑟𝑖𝑐𝑒,𝑤𝑝𝑜)=𝐸𝐹_𝑐×𝑆𝐹_𝑤×𝑆𝐹_𝑝×𝑆𝐹_𝑜</a:t>
               </a:r>
-              <a:endParaRPr lang="en-AU" sz="1100"/>
+              <a:endParaRPr lang="en-AU" sz="1000"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -6154,7 +6103,7 @@
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMath>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
                       <m:t>𝑆</m:t>
@@ -6162,14 +6111,14 @@
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:sSubPr>
                       <m:e>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝐹</m:t>
@@ -6177,7 +6126,7 @@
                       </m:e>
                       <m:sub>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝑜</m:t>
@@ -6185,7 +6134,7 @@
                       </m:sub>
                     </m:sSub>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
                       <m:t>=(1+</m:t>
@@ -6193,7 +6142,7 @@
                     <m:sSup>
                       <m:sSupPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
@@ -6202,7 +6151,7 @@
                         <m:d>
                           <m:dPr>
                             <m:ctrlPr>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                             </m:ctrlPr>
@@ -6211,14 +6160,14 @@
                             <m:d>
                               <m:dPr>
                                 <m:ctrlPr>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                 </m:ctrlPr>
                               </m:dPr>
                               <m:e>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝑅𝑂</m:t>
@@ -6226,14 +6175,14 @@
                                 <m:sSub>
                                   <m:sSubPr>
                                     <m:ctrlPr>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                     </m:ctrlPr>
                                   </m:sSubPr>
                                   <m:e>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝐴</m:t>
@@ -6241,7 +6190,7 @@
                                   </m:e>
                                   <m:sub>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝑜</m:t>
@@ -6249,13 +6198,13 @@
                                   </m:sub>
                                 </m:sSub>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>1×</m:t>
                                 </m:r>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝐶𝐹𝑂</m:t>
@@ -6263,14 +6212,14 @@
                                 <m:sSub>
                                   <m:sSubPr>
                                     <m:ctrlPr>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                     </m:ctrlPr>
                                   </m:sSubPr>
                                   <m:e>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝐴</m:t>
@@ -6278,7 +6227,7 @@
                                   </m:e>
                                   <m:sub>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝑜</m:t>
@@ -6286,7 +6235,7 @@
                                   </m:sub>
                                 </m:sSub>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>1</m:t>
@@ -6294,7 +6243,7 @@
                               </m:e>
                             </m:d>
                             <m:r>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                               <m:t>+</m:t>
@@ -6302,14 +6251,14 @@
                             <m:d>
                               <m:dPr>
                                 <m:ctrlPr>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                 </m:ctrlPr>
                               </m:dPr>
                               <m:e>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝑅𝑂</m:t>
@@ -6317,14 +6266,14 @@
                                 <m:sSub>
                                   <m:sSubPr>
                                     <m:ctrlPr>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                     </m:ctrlPr>
                                   </m:sSubPr>
                                   <m:e>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝐴</m:t>
@@ -6332,7 +6281,7 @@
                                   </m:e>
                                   <m:sub>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝑜</m:t>
@@ -6340,13 +6289,13 @@
                                   </m:sub>
                                 </m:sSub>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>2×</m:t>
                                 </m:r>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝐶𝐹𝑂</m:t>
@@ -6354,14 +6303,14 @@
                                 <m:sSub>
                                   <m:sSubPr>
                                     <m:ctrlPr>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                     </m:ctrlPr>
                                   </m:sSubPr>
                                   <m:e>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝐴</m:t>
@@ -6369,7 +6318,7 @@
                                   </m:e>
                                   <m:sub>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝑜</m:t>
@@ -6377,7 +6326,7 @@
                                   </m:sub>
                                 </m:sSub>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>2</m:t>
@@ -6385,7 +6334,7 @@
                               </m:e>
                             </m:d>
                             <m:r>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                               <m:t>+</m:t>
@@ -6393,14 +6342,14 @@
                             <m:d>
                               <m:dPr>
                                 <m:ctrlPr>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                 </m:ctrlPr>
                               </m:dPr>
                               <m:e>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝑅𝑂</m:t>
@@ -6408,14 +6357,14 @@
                                 <m:sSub>
                                   <m:sSubPr>
                                     <m:ctrlPr>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                     </m:ctrlPr>
                                   </m:sSubPr>
                                   <m:e>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝐴</m:t>
@@ -6423,7 +6372,7 @@
                                   </m:e>
                                   <m:sub>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝑜</m:t>
@@ -6431,13 +6380,13 @@
                                   </m:sub>
                                 </m:sSub>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>3×</m:t>
                                 </m:r>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝐶𝐹𝑂</m:t>
@@ -6445,14 +6394,14 @@
                                 <m:sSub>
                                   <m:sSubPr>
                                     <m:ctrlPr>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                     </m:ctrlPr>
                                   </m:sSubPr>
                                   <m:e>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝐴</m:t>
@@ -6460,7 +6409,7 @@
                                   </m:e>
                                   <m:sub>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝑜</m:t>
@@ -6468,7 +6417,7 @@
                                   </m:sub>
                                 </m:sSub>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>3</m:t>
@@ -6476,7 +6425,7 @@
                               </m:e>
                             </m:d>
                             <m:r>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                               <m:t>+</m:t>
@@ -6484,14 +6433,14 @@
                             <m:d>
                               <m:dPr>
                                 <m:ctrlPr>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                 </m:ctrlPr>
                               </m:dPr>
                               <m:e>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝑅𝑂</m:t>
@@ -6499,14 +6448,14 @@
                                 <m:sSub>
                                   <m:sSubPr>
                                     <m:ctrlPr>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                     </m:ctrlPr>
                                   </m:sSubPr>
                                   <m:e>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝐴</m:t>
@@ -6514,7 +6463,7 @@
                                   </m:e>
                                   <m:sub>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝑜</m:t>
@@ -6522,13 +6471,13 @@
                                   </m:sub>
                                 </m:sSub>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>4×</m:t>
                                 </m:r>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝐶𝐹𝑂</m:t>
@@ -6536,14 +6485,14 @@
                                 <m:sSub>
                                   <m:sSubPr>
                                     <m:ctrlPr>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                     </m:ctrlPr>
                                   </m:sSubPr>
                                   <m:e>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝐴</m:t>
@@ -6551,7 +6500,7 @@
                                   </m:e>
                                   <m:sub>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝑜</m:t>
@@ -6559,7 +6508,7 @@
                                   </m:sub>
                                 </m:sSub>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>4</m:t>
@@ -6567,7 +6516,7 @@
                               </m:e>
                             </m:d>
                             <m:r>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                               <m:t>+</m:t>
@@ -6575,14 +6524,14 @@
                             <m:d>
                               <m:dPr>
                                 <m:ctrlPr>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                 </m:ctrlPr>
                               </m:dPr>
                               <m:e>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝑅𝑂</m:t>
@@ -6590,14 +6539,14 @@
                                 <m:sSub>
                                   <m:sSubPr>
                                     <m:ctrlPr>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                     </m:ctrlPr>
                                   </m:sSubPr>
                                   <m:e>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝐴</m:t>
@@ -6605,7 +6554,7 @@
                                   </m:e>
                                   <m:sub>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝑜</m:t>
@@ -6613,13 +6562,13 @@
                                   </m:sub>
                                 </m:sSub>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>5×</m:t>
                                 </m:r>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝐶𝐹𝑂</m:t>
@@ -6627,14 +6576,14 @@
                                 <m:sSub>
                                   <m:sSubPr>
                                     <m:ctrlPr>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                     </m:ctrlPr>
                                   </m:sSubPr>
                                   <m:e>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝐴</m:t>
@@ -6642,7 +6591,7 @@
                                   </m:e>
                                   <m:sub>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝑜</m:t>
@@ -6650,7 +6599,7 @@
                                   </m:sub>
                                 </m:sSub>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>5</m:t>
@@ -6658,7 +6607,7 @@
                               </m:e>
                             </m:d>
                             <m:r>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                               <m:t>+</m:t>
@@ -6666,14 +6615,14 @@
                             <m:d>
                               <m:dPr>
                                 <m:ctrlPr>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                 </m:ctrlPr>
                               </m:dPr>
                               <m:e>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝑅𝑂</m:t>
@@ -6681,14 +6630,14 @@
                                 <m:sSub>
                                   <m:sSubPr>
                                     <m:ctrlPr>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                     </m:ctrlPr>
                                   </m:sSubPr>
                                   <m:e>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝐴</m:t>
@@ -6696,7 +6645,7 @@
                                   </m:e>
                                   <m:sub>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝑜</m:t>
@@ -6704,13 +6653,13 @@
                                   </m:sub>
                                 </m:sSub>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>6×</m:t>
                                 </m:r>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝐶𝐹𝑂</m:t>
@@ -6718,14 +6667,14 @@
                                 <m:sSub>
                                   <m:sSubPr>
                                     <m:ctrlPr>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                     </m:ctrlPr>
                                   </m:sSubPr>
                                   <m:e>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝐴</m:t>
@@ -6733,7 +6682,7 @@
                                   </m:e>
                                   <m:sub>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝑜</m:t>
@@ -6741,7 +6690,7 @@
                                   </m:sub>
                                 </m:sSub>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>6</m:t>
@@ -6753,7 +6702,7 @@
                       </m:e>
                       <m:sup>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>0.59</m:t>
@@ -6763,7 +6712,7 @@
                   </m:oMath>
                 </m:oMathPara>
               </a14:m>
-              <a:endParaRPr lang="en-AU" sz="1100"/>
+              <a:endParaRPr lang="en-AU" sz="1000"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -6812,12 +6761,12 @@
             <a:p>
               <a:pPr/>
               <a:r>
-                <a:rPr lang="en-AU" sz="1100" i="0">
+                <a:rPr lang="en-AU" sz="1000" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
                 <a:t>𝑆𝐹_𝑜=(1+((𝑅𝑂𝐴_𝑜 1×𝐶𝐹𝑂𝐴_𝑜 1)+(𝑅𝑂𝐴_𝑜 2×𝐶𝐹𝑂𝐴_𝑜 2)+(𝑅𝑂𝐴_𝑜 3×𝐶𝐹𝑂𝐴_𝑜 3)+(𝑅𝑂𝐴_𝑜 4×𝐶𝐹𝑂𝐴_𝑜 4)+(𝑅𝑂𝐴_𝑜 5×𝐶𝐹𝑂𝐴_𝑜 5)+(𝑅𝑂𝐴_𝑜 6×𝐶𝐹𝑂𝐴_𝑜 6))^0.59</a:t>
               </a:r>
-              <a:endParaRPr lang="en-AU" sz="1100"/>
+              <a:endParaRPr lang="en-AU" sz="1000"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -6883,14 +6832,14 @@
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:sSubPr>
                       <m:e>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝐸</m:t>
@@ -6898,7 +6847,7 @@
                       </m:e>
                       <m:sub>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝑟𝑖𝑐𝑒</m:t>
@@ -6906,7 +6855,7 @@
                       </m:sub>
                     </m:sSub>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
                       <m:t>=</m:t>
@@ -6916,14 +6865,14 @@
                         <m:chr m:val="∑"/>
                         <m:supHide m:val="on"/>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:naryPr>
                       <m:sub>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝑤</m:t>
@@ -6936,14 +6885,14 @@
                             <m:chr m:val="∑"/>
                             <m:supHide m:val="on"/>
                             <m:ctrlPr>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                             </m:ctrlPr>
                           </m:naryPr>
                           <m:sub>
                             <m:r>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                               <m:t>𝑝</m:t>
@@ -6956,14 +6905,14 @@
                                 <m:chr m:val="∑"/>
                                 <m:supHide m:val="on"/>
                                 <m:ctrlPr>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                 </m:ctrlPr>
                               </m:naryPr>
                               <m:sub>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝑜</m:t>
@@ -6974,7 +6923,7 @@
                                 <m:d>
                                   <m:dPr>
                                     <m:ctrlPr>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                     </m:ctrlPr>
@@ -6983,14 +6932,14 @@
                                     <m:sSub>
                                       <m:sSubPr>
                                         <m:ctrlPr>
-                                          <a:rPr lang="en-AU" sz="1100" i="1">
+                                          <a:rPr lang="en-AU" sz="1000" i="1">
                                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                           </a:rPr>
                                         </m:ctrlPr>
                                       </m:sSubPr>
                                       <m:e>
                                         <m:r>
-                                          <a:rPr lang="en-AU" sz="1100" i="1">
+                                          <a:rPr lang="en-AU" sz="1000" i="1">
                                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                           </a:rPr>
                                           <m:t>𝐴</m:t>
@@ -6998,19 +6947,19 @@
                                       </m:e>
                                       <m:sub>
                                         <m:r>
-                                          <a:rPr lang="en-AU" sz="1100" i="1">
+                                          <a:rPr lang="en-AU" sz="1000" i="1">
                                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                           </a:rPr>
                                           <m:t>𝑟𝑖𝑐𝑒</m:t>
                                         </m:r>
                                         <m:r>
-                                          <a:rPr lang="en-AU" sz="1100" i="1">
+                                          <a:rPr lang="en-AU" sz="1000" i="1">
                                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                           </a:rPr>
                                           <m:t>,</m:t>
                                         </m:r>
                                         <m:r>
-                                          <a:rPr lang="en-AU" sz="1100" i="1">
+                                          <a:rPr lang="en-AU" sz="1000" i="1">
                                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                           </a:rPr>
                                           <m:t>𝑤𝑝𝑜</m:t>
@@ -7018,13 +6967,13 @@
                                       </m:sub>
                                     </m:sSub>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>×</m:t>
                                     </m:r>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝐸</m:t>
@@ -7032,14 +6981,14 @@
                                     <m:sSub>
                                       <m:sSubPr>
                                         <m:ctrlPr>
-                                          <a:rPr lang="en-AU" sz="1100" i="1">
+                                          <a:rPr lang="en-AU" sz="1000" i="1">
                                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                           </a:rPr>
                                         </m:ctrlPr>
                                       </m:sSubPr>
                                       <m:e>
                                         <m:r>
-                                          <a:rPr lang="en-AU" sz="1100" i="1">
+                                          <a:rPr lang="en-AU" sz="1000" i="1">
                                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                           </a:rPr>
                                           <m:t>𝐹</m:t>
@@ -7047,19 +6996,19 @@
                                       </m:e>
                                       <m:sub>
                                         <m:r>
-                                          <a:rPr lang="en-AU" sz="1100" i="1">
+                                          <a:rPr lang="en-AU" sz="1000" i="1">
                                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                           </a:rPr>
                                           <m:t>𝑟𝑖𝑐𝑒</m:t>
                                         </m:r>
                                         <m:r>
-                                          <a:rPr lang="en-AU" sz="1100" i="1">
+                                          <a:rPr lang="en-AU" sz="1000" i="1">
                                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                           </a:rPr>
                                           <m:t>,</m:t>
                                         </m:r>
                                         <m:r>
-                                          <a:rPr lang="en-AU" sz="1100" i="1">
+                                          <a:rPr lang="en-AU" sz="1000" i="1">
                                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                           </a:rPr>
                                           <m:t>𝑤𝑝𝑜</m:t>
@@ -7067,7 +7016,7 @@
                                       </m:sub>
                                     </m:sSub>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>×</m:t>
@@ -7075,14 +7024,14 @@
                                     <m:sSub>
                                       <m:sSubPr>
                                         <m:ctrlPr>
-                                          <a:rPr lang="en-AU" sz="1100" i="1">
+                                          <a:rPr lang="en-AU" sz="1000" i="1">
                                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                           </a:rPr>
                                         </m:ctrlPr>
                                       </m:sSubPr>
                                       <m:e>
                                         <m:r>
-                                          <a:rPr lang="en-AU" sz="1100" i="1">
+                                          <a:rPr lang="en-AU" sz="1000" i="1">
                                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                           </a:rPr>
                                           <m:t>𝑡</m:t>
@@ -7090,19 +7039,19 @@
                                       </m:e>
                                       <m:sub>
                                         <m:r>
-                                          <a:rPr lang="en-AU" sz="1100" i="1">
+                                          <a:rPr lang="en-AU" sz="1000" i="1">
                                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                           </a:rPr>
                                           <m:t>𝑟𝑖𝑐𝑒</m:t>
                                         </m:r>
                                         <m:r>
-                                          <a:rPr lang="en-AU" sz="1100" i="1">
+                                          <a:rPr lang="en-AU" sz="1000" i="1">
                                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                           </a:rPr>
                                           <m:t>,</m:t>
                                         </m:r>
                                         <m:r>
-                                          <a:rPr lang="en-AU" sz="1100" i="1">
+                                          <a:rPr lang="en-AU" sz="1000" i="1">
                                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                           </a:rPr>
                                           <m:t>𝑤𝑝𝑜</m:t>
@@ -7118,7 +7067,7 @@
                       </m:e>
                     </m:nary>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
                       <m:t>×</m:t>
@@ -7126,14 +7075,14 @@
                     <m:sSup>
                       <m:sSupPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:sSupPr>
                       <m:e>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>10</m:t>
@@ -7141,7 +7090,7 @@
                       </m:e>
                       <m:sup>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>−3</m:t>
@@ -7151,7 +7100,7 @@
                   </m:oMath>
                 </m:oMathPara>
               </a14:m>
-              <a:endParaRPr lang="en-AU" sz="1100"/>
+              <a:endParaRPr lang="en-AU" sz="1000"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -7199,12 +7148,12 @@
             <a:lstStyle/>
             <a:p>
               <a:r>
-                <a:rPr lang="en-AU" sz="1100" i="0">
+                <a:rPr lang="en-AU" sz="1000" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
                 <a:t>𝐸_𝑟𝑖𝑐𝑒=∑8_𝑤▒∑8_𝑝▒∑8_𝑜▒(𝐴_(𝑟𝑖𝑐𝑒,𝑤𝑝𝑜)×𝐸𝐹_(𝑟𝑖𝑐𝑒,𝑤𝑝𝑜)×𝑡_(𝑟𝑖𝑐𝑒,𝑤𝑝𝑜) ) ×10^(−3)</a:t>
               </a:r>
-              <a:endParaRPr lang="en-AU" sz="1100"/>
+              <a:endParaRPr lang="en-AU" sz="1000"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -7992,12 +7941,12 @@
     </a:clrScheme>
     <a:fontScheme name="Custom 1">
       <a:majorFont>
-        <a:latin typeface="Times New Roman"/>
+        <a:latin typeface="Arial"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Times New Roman"/>
+        <a:latin typeface="Arial"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -8208,31 +8157,31 @@
     <tabColor rgb="FF0C769E"/>
   </sheetPr>
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25" ht="30" customHeight="1">
       <c r="A1" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A3" s="119" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A6" s="118" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="A7" s="17" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="A8" s="17" t="str">
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
@@ -8249,7 +8198,7 @@
     <tabColor rgb="FF0C769E"/>
   </sheetPr>
   <dimension ref="A1:AV45"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -8303,7 +8252,7 @@
       <c r="AN1" s="112"/>
       <c r="AO1" s="112"/>
     </row>
-    <row r="2" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C2" s="112"/>
       <c r="D2" s="112"/>
       <c r="E2" s="112"/>
@@ -8345,7 +8294,7 @@
       <c r="AO2" s="112"/>
       <c r="AP2" s="113"/>
     </row>
-    <row r="3" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -8390,13 +8339,13 @@
       <c r="AN3" s="114"/>
       <c r="AO3" s="114"/>
     </row>
-    <row r="4" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="98" t="str">
         <f>HYPERLINK("#'Overview'!A1", "Overview")</f>
         <v>Overview</v>
       </c>
     </row>
-    <row r="5" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
@@ -8416,7 +8365,7 @@
       <c r="N5" s="78"/>
       <c r="O5" s="74"/>
     </row>
-    <row r="6" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D6" s="115" t="s">
         <v>102</v>
       </c>
@@ -8432,84 +8381,84 @@
       <c r="N6" s="77"/>
       <c r="O6" s="75"/>
     </row>
-    <row r="7" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="str">
         <f>HYPERLINK("#'Input - Site'!A1", "Site")</f>
         <v>Site</v>
       </c>
     </row>
-    <row r="10" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="str">
         <f>HYPERLINK("#'Input - Rice'!A1", "Rice")</f>
         <v>Rice</v>
       </c>
     </row>
-    <row r="11" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="str">
         <f>HYPERLINK("#'7.1.1-2 Rice cultivation'!A1", "7.1.1-2 Rice cultivation")</f>
         <v>7.1.1-2 Rice cultivation</v>
       </c>
     </row>
-    <row r="15" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="118" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="str">
         <f>HYPERLINK("#'Constants - Rice cultivation'!A1", "Constants - Rice cultivation")</f>
         <v>Constants - Rice cultivation</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" spans="12:48" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" spans="12:48" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="12:48" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="12:48" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="12:48" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="12:48" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="12:48" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="12:48" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="12:48" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="12:48" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L37" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="38" spans="12:48" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="12:48" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="12:48" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="12:48" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="12:48" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="12:48" x14ac:dyDescent="0.25">
+    <row r="38" spans="12:48" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="12:48" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="12:48" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="12:48" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="12:48" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="12:48" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="AV45" t="s">
         <v>100</v>
       </c>
@@ -8527,7 +8476,7 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:K87"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="3" width="2.7109375" customWidth="1"/>
@@ -8548,10 +8497,10 @@
         <v>166</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C2" s="9"/>
     </row>
-    <row r="3" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -8566,7 +8515,7 @@
       <c r="J3" s="21"/>
       <c r="K3" s="21"/>
     </row>
-    <row r="4" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="str">
         <f>HYPERLINK("#'Overview'!A1", "Overview")</f>
         <v>Overview</v>
@@ -8583,7 +8532,7 @@
       <c r="J4" s="6"/>
       <c r="K4" s="24"/>
     </row>
-    <row r="5" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="98" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
@@ -8598,7 +8547,7 @@
       <c r="J5" s="21"/>
       <c r="K5" s="21"/>
     </row>
-    <row r="6" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C6" s="21"/>
       <c r="D6" s="80" t="s">
         <v>98</v>
@@ -8611,7 +8560,7 @@
       <c r="J6" s="21"/>
       <c r="K6" s="21"/>
     </row>
-    <row r="7" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C7" s="21"/>
       <c r="D7" s="21"/>
       <c r="E7" s="21"/>
@@ -8622,7 +8571,7 @@
       <c r="J7" s="21"/>
       <c r="K7" s="21"/>
     </row>
-    <row r="8" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
         <v>0</v>
       </c>
@@ -8650,7 +8599,7 @@
       </c>
       <c r="K8" s="21"/>
     </row>
-    <row r="9" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="str">
         <f>HYPERLINK("#'Input - Site'!A1", "Site")</f>
         <v>Site</v>
@@ -8683,7 +8632,7 @@
       </c>
       <c r="K9" s="21"/>
     </row>
-    <row r="10" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="str">
         <f>HYPERLINK("#'Input - Rice'!A1", "Rice")</f>
         <v>Rice</v>
@@ -8708,7 +8657,7 @@
       </c>
       <c r="K10" s="21"/>
     </row>
-    <row r="11" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C11" s="21"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
@@ -8719,7 +8668,7 @@
       <c r="J11" s="1"/>
       <c r="K11" s="21"/>
     </row>
-    <row r="12" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C12" s="21"/>
       <c r="D12" s="89"/>
       <c r="E12" s="89"/>
@@ -8730,7 +8679,7 @@
       <c r="J12" s="89"/>
       <c r="K12" s="21"/>
     </row>
-    <row r="13" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>51</v>
       </c>
@@ -8744,7 +8693,7 @@
       <c r="J13" s="21"/>
       <c r="K13" s="21"/>
     </row>
-    <row r="14" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="str">
         <f>HYPERLINK("#'7.1.1-2 Rice cultivation'!A1", "7.1.1-2 Rice cultivation")</f>
         <v>7.1.1-2 Rice cultivation</v>
@@ -8759,7 +8708,7 @@
       <c r="J14" s="21"/>
       <c r="K14" s="21"/>
     </row>
-    <row r="15" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C15" s="21"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
@@ -8770,7 +8719,7 @@
       <c r="J15" s="21"/>
       <c r="K15" s="21"/>
     </row>
-    <row r="16" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C16" s="21"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
@@ -8781,7 +8730,7 @@
       <c r="J16" s="21"/>
       <c r="K16" s="21"/>
     </row>
-    <row r="17" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="118" t="s">
         <v>1</v>
       </c>
@@ -8795,7 +8744,7 @@
       <c r="J17" s="21"/>
       <c r="K17" s="21"/>
     </row>
-    <row r="18" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="str">
         <f>HYPERLINK("#'Constants - Rice cultivation'!A1", "Constants - Rice cultivation")</f>
         <v>Constants - Rice cultivation</v>
@@ -8810,7 +8759,7 @@
       <c r="J18" s="1"/>
       <c r="K18" s="21"/>
     </row>
-    <row r="19" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
@@ -8825,7 +8774,7 @@
       <c r="J19" s="1"/>
       <c r="K19" s="21"/>
     </row>
-    <row r="20" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C20" s="21"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
@@ -8836,7 +8785,7 @@
       <c r="J20" s="1"/>
       <c r="K20" s="21"/>
     </row>
-    <row r="21" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="21"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
@@ -8847,7 +8796,7 @@
       <c r="J21" s="1"/>
       <c r="K21" s="21"/>
     </row>
-    <row r="22" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="21"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
@@ -8858,7 +8807,7 @@
       <c r="J22" s="1"/>
       <c r="K22" s="21"/>
     </row>
-    <row r="23" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C23" s="21"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
@@ -8869,7 +8818,7 @@
       <c r="J23" s="1"/>
       <c r="K23" s="21"/>
     </row>
-    <row r="24" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C24" s="21"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
@@ -8880,7 +8829,7 @@
       <c r="J24" s="1"/>
       <c r="K24" s="21"/>
     </row>
-    <row r="25" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C25" s="21"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
@@ -8891,7 +8840,7 @@
       <c r="J25" s="21"/>
       <c r="K25" s="21"/>
     </row>
-    <row r="26" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C26" s="21"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
@@ -8902,7 +8851,7 @@
       <c r="J26" s="21"/>
       <c r="K26" s="21"/>
     </row>
-    <row r="27" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C27" s="21"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
@@ -8913,7 +8862,7 @@
       <c r="J27" s="21"/>
       <c r="K27" s="21"/>
     </row>
-    <row r="28" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C28" s="21"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
@@ -8924,7 +8873,7 @@
       <c r="J28" s="21"/>
       <c r="K28" s="21"/>
     </row>
-    <row r="29" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C29" s="21"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
@@ -8935,7 +8884,7 @@
       <c r="J29" s="21"/>
       <c r="K29" s="21"/>
     </row>
-    <row r="30" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C30" s="21"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
@@ -8946,7 +8895,7 @@
       <c r="J30" s="21"/>
       <c r="K30" s="21"/>
     </row>
-    <row r="31" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C31" s="21"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
@@ -8957,7 +8906,7 @@
       <c r="J31" s="21"/>
       <c r="K31" s="21"/>
     </row>
-    <row r="32" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C32" s="21"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
@@ -8968,7 +8917,7 @@
       <c r="J32" s="21"/>
       <c r="K32" s="21"/>
     </row>
-    <row r="33" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C33" s="21"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
@@ -8979,7 +8928,7 @@
       <c r="J33" s="21"/>
       <c r="K33" s="21"/>
     </row>
-    <row r="34" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C34" s="21"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
@@ -8990,7 +8939,7 @@
       <c r="J34" s="21"/>
       <c r="K34" s="21"/>
     </row>
-    <row r="35" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C35" s="21"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
@@ -9001,7 +8950,7 @@
       <c r="J35" s="21"/>
       <c r="K35" s="21"/>
     </row>
-    <row r="36" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C36" s="21"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
@@ -9012,7 +8961,7 @@
       <c r="J36" s="21"/>
       <c r="K36" s="21"/>
     </row>
-    <row r="37" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C37" s="21"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
@@ -9023,7 +8972,7 @@
       <c r="J37" s="21"/>
       <c r="K37" s="21"/>
     </row>
-    <row r="38" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C38" s="21"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
@@ -9034,7 +8983,7 @@
       <c r="J38" s="90"/>
       <c r="K38" s="21"/>
     </row>
-    <row r="39" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C39" s="21"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
@@ -9045,7 +8994,7 @@
       <c r="J39" s="90"/>
       <c r="K39" s="21"/>
     </row>
-    <row r="40" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C40" s="21"/>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
@@ -9056,7 +9005,7 @@
       <c r="J40" s="90"/>
       <c r="K40" s="21"/>
     </row>
-    <row r="41" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C41" s="21"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
@@ -9067,7 +9016,7 @@
       <c r="J41" s="90"/>
       <c r="K41" s="21"/>
     </row>
-    <row r="42" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C42" s="21"/>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
@@ -9078,7 +9027,7 @@
       <c r="J42" s="90"/>
       <c r="K42" s="21"/>
     </row>
-    <row r="43" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C43" s="21"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
@@ -9089,7 +9038,7 @@
       <c r="J43" s="90"/>
       <c r="K43" s="21"/>
     </row>
-    <row r="44" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C44" s="21"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
@@ -9100,7 +9049,7 @@
       <c r="J44" s="90"/>
       <c r="K44" s="21"/>
     </row>
-    <row r="45" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C45" s="21"/>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
@@ -9111,7 +9060,7 @@
       <c r="J45" s="90"/>
       <c r="K45" s="21"/>
     </row>
-    <row r="46" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C46" s="21"/>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
@@ -9122,7 +9071,7 @@
       <c r="J46" s="90"/>
       <c r="K46" s="21"/>
     </row>
-    <row r="47" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C47" s="21"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
@@ -9133,7 +9082,7 @@
       <c r="J47" s="90"/>
       <c r="K47" s="21"/>
     </row>
-    <row r="48" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C48" s="21"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
@@ -9144,7 +9093,7 @@
       <c r="J48" s="90"/>
       <c r="K48" s="21"/>
     </row>
-    <row r="49" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C49" s="21"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
@@ -9155,7 +9104,7 @@
       <c r="J49" s="90"/>
       <c r="K49" s="21"/>
     </row>
-    <row r="50" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C50" s="21"/>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
@@ -9166,7 +9115,7 @@
       <c r="J50" s="90"/>
       <c r="K50" s="21"/>
     </row>
-    <row r="51" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C51" s="21"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
@@ -9177,7 +9126,7 @@
       <c r="J51" s="90"/>
       <c r="K51" s="21"/>
     </row>
-    <row r="52" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C52" s="21"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
@@ -9188,7 +9137,7 @@
       <c r="J52" s="90"/>
       <c r="K52" s="21"/>
     </row>
-    <row r="53" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C53" s="21"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
@@ -9199,7 +9148,7 @@
       <c r="J53" s="90"/>
       <c r="K53" s="21"/>
     </row>
-    <row r="54" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C54" s="21"/>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
@@ -9210,7 +9159,7 @@
       <c r="J54" s="21"/>
       <c r="K54" s="21"/>
     </row>
-    <row r="55" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C55" s="21"/>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
@@ -9221,7 +9170,7 @@
       <c r="J55" s="21"/>
       <c r="K55" s="21"/>
     </row>
-    <row r="56" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C56" s="21"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
@@ -9232,7 +9181,7 @@
       <c r="J56" s="21"/>
       <c r="K56" s="21"/>
     </row>
-    <row r="57" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C57" s="21"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
@@ -9243,7 +9192,7 @@
       <c r="J57" s="21"/>
       <c r="K57" s="21"/>
     </row>
-    <row r="58" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C58" s="21"/>
       <c r="D58" s="1"/>
       <c r="E58" s="29"/>
@@ -9254,7 +9203,7 @@
       <c r="J58" s="21"/>
       <c r="K58" s="21"/>
     </row>
-    <row r="59" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C59" s="21"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
@@ -9265,7 +9214,7 @@
       <c r="J59" s="1"/>
       <c r="K59" s="21"/>
     </row>
-    <row r="60" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C60" s="21"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
@@ -9276,7 +9225,7 @@
       <c r="J60" s="1"/>
       <c r="K60" s="21"/>
     </row>
-    <row r="61" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C61" s="21"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
@@ -9287,7 +9236,7 @@
       <c r="J61" s="1"/>
       <c r="K61" s="21"/>
     </row>
-    <row r="62" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C62" s="21"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
@@ -9298,7 +9247,7 @@
       <c r="J62" s="1"/>
       <c r="K62" s="21"/>
     </row>
-    <row r="63" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C63" s="21"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
@@ -9309,7 +9258,7 @@
       <c r="J63" s="1"/>
       <c r="K63" s="21"/>
     </row>
-    <row r="64" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C64" s="21"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
@@ -9320,7 +9269,7 @@
       <c r="J64" s="1"/>
       <c r="K64" s="21"/>
     </row>
-    <row r="65" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C65" s="21"/>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
@@ -9331,7 +9280,7 @@
       <c r="J65" s="1"/>
       <c r="K65" s="21"/>
     </row>
-    <row r="66" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C66" s="21"/>
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
@@ -9342,7 +9291,7 @@
       <c r="J66" s="1"/>
       <c r="K66" s="21"/>
     </row>
-    <row r="67" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C67" s="21"/>
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
@@ -9353,7 +9302,7 @@
       <c r="J67" s="1"/>
       <c r="K67" s="21"/>
     </row>
-    <row r="68" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C68" s="21"/>
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
@@ -9364,7 +9313,7 @@
       <c r="J68" s="1"/>
       <c r="K68" s="21"/>
     </row>
-    <row r="69" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C69" s="21"/>
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
@@ -9375,7 +9324,7 @@
       <c r="J69" s="1"/>
       <c r="K69" s="21"/>
     </row>
-    <row r="70" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C70" s="21"/>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
@@ -9386,7 +9335,7 @@
       <c r="J70" s="1"/>
       <c r="K70" s="21"/>
     </row>
-    <row r="71" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C71" s="21"/>
       <c r="D71" s="1"/>
       <c r="E71" s="1"/>
@@ -9397,7 +9346,7 @@
       <c r="J71" s="1"/>
       <c r="K71" s="21"/>
     </row>
-    <row r="72" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C72" s="21"/>
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
@@ -9408,7 +9357,7 @@
       <c r="J72" s="1"/>
       <c r="K72" s="21"/>
     </row>
-    <row r="73" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C73" s="21"/>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
@@ -9419,7 +9368,7 @@
       <c r="J73" s="1"/>
       <c r="K73" s="21"/>
     </row>
-    <row r="74" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C74" s="21"/>
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
@@ -9430,7 +9379,7 @@
       <c r="J74" s="1"/>
       <c r="K74" s="21"/>
     </row>
-    <row r="75" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C75" s="21"/>
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
@@ -9441,7 +9390,7 @@
       <c r="J75" s="1"/>
       <c r="K75" s="21"/>
     </row>
-    <row r="76" spans="3:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="3:11" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C76" s="21"/>
       <c r="D76" s="1"/>
       <c r="E76" s="1"/>
@@ -9452,7 +9401,7 @@
       <c r="J76" s="1"/>
       <c r="K76" s="21"/>
     </row>
-    <row r="77" spans="3:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="3:11" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C77" s="21"/>
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
@@ -9463,7 +9412,7 @@
       <c r="J77" s="1"/>
       <c r="K77" s="21"/>
     </row>
-    <row r="78" spans="3:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="3:11" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C78" s="21"/>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
@@ -9474,7 +9423,7 @@
       <c r="J78" s="1"/>
       <c r="K78" s="21"/>
     </row>
-    <row r="79" spans="3:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="3:11" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C79" s="21"/>
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
@@ -9485,7 +9434,7 @@
       <c r="J79" s="1"/>
       <c r="K79" s="21"/>
     </row>
-    <row r="80" spans="3:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="3:11" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C80" s="21"/>
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
@@ -9496,7 +9445,7 @@
       <c r="J80" s="1"/>
       <c r="K80" s="21"/>
     </row>
-    <row r="81" spans="3:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="3:11" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C81" s="21"/>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
@@ -9507,7 +9456,7 @@
       <c r="J81" s="1"/>
       <c r="K81" s="21"/>
     </row>
-    <row r="82" spans="3:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="3:11" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C82" s="21"/>
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
@@ -9518,7 +9467,7 @@
       <c r="J82" s="1"/>
       <c r="K82" s="21"/>
     </row>
-    <row r="83" spans="3:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="3:11" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C83" s="21"/>
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
@@ -9529,7 +9478,7 @@
       <c r="J83" s="1"/>
       <c r="K83" s="21"/>
     </row>
-    <row r="84" spans="3:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="3:11" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C84" s="21"/>
       <c r="D84" s="1"/>
       <c r="E84" s="1"/>
@@ -9540,7 +9489,7 @@
       <c r="J84" s="1"/>
       <c r="K84" s="21"/>
     </row>
-    <row r="85" spans="3:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="3:11" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C85" s="21"/>
       <c r="D85" s="1"/>
       <c r="E85" s="1"/>
@@ -9551,7 +9500,7 @@
       <c r="J85" s="1"/>
       <c r="K85" s="21"/>
     </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="86" spans="3:11" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="C86" s="21"/>
       <c r="D86" s="21"/>
       <c r="E86" s="21"/>
@@ -9562,7 +9511,7 @@
       <c r="J86" s="21"/>
       <c r="K86" s="21"/>
     </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="87" spans="3:11" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="C87" s="21"/>
       <c r="D87" s="21"/>
       <c r="E87" s="21"/>
@@ -9586,7 +9535,7 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:AA160"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="16" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" style="7" customWidth="1"/>
@@ -9607,7 +9556,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:24" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2"/>
       <c r="C2" s="9"/>
       <c r="D2" s="9"/>
@@ -9618,7 +9567,7 @@
       <c r="I2" s="9"/>
       <c r="J2" s="9"/>
     </row>
-    <row r="3" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -9645,7 +9594,7 @@
       <c r="W3" s="11"/>
       <c r="X3" s="11"/>
     </row>
-    <row r="4" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="str">
         <f>HYPERLINK("#'Overview'!A1", "Overview")</f>
         <v>Overview</v>
@@ -9660,7 +9609,7 @@
       <c r="J4" s="57"/>
       <c r="K4" s="57"/>
     </row>
-    <row r="5" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
@@ -9670,12 +9619,12 @@
       </c>
       <c r="N5" s="37"/>
     </row>
-    <row r="6" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6"/>
       <c r="D6" s="14"/>
       <c r="N6" s="38"/>
     </row>
-    <row r="7" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7"/>
       <c r="D7" s="1" t="s">
         <v>4</v>
@@ -9685,7 +9634,7 @@
       </c>
       <c r="F7" s="2"/>
     </row>
-    <row r="8" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
         <v>0</v>
       </c>
@@ -9696,14 +9645,14 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="97" t="str">
         <f>HYPERLINK("#'Input - Site'!A1", "Site")</f>
         <v>Site</v>
       </c>
       <c r="N9" s="39"/>
     </row>
-    <row r="10" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="str">
         <f>HYPERLINK("#'Input - Rice'!A1", "Rice")</f>
         <v>Rice</v>
@@ -9716,11 +9665,11 @@
       <c r="G10" s="76"/>
       <c r="N10" s="39"/>
     </row>
-    <row r="11" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11"/>
       <c r="N11" s="40"/>
     </row>
-    <row r="12" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12"/>
       <c r="D12" s="10" t="s">
         <v>57</v>
@@ -9732,7 +9681,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>51</v>
       </c>
@@ -9749,7 +9698,7 @@
       <c r="N13" s="35"/>
       <c r="O13" s="35"/>
     </row>
-    <row r="14" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="str">
         <f>HYPERLINK("#'7.1.1-2 Rice cultivation'!A1", "7.1.1-2 Rice cultivation")</f>
         <v>7.1.1-2 Rice cultivation</v>
@@ -9757,7 +9706,7 @@
       <c r="N14" s="35"/>
       <c r="O14" s="35"/>
     </row>
-    <row r="15" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
@@ -9767,7 +9716,7 @@
       <c r="N15" s="35"/>
       <c r="O15" s="35"/>
     </row>
-    <row r="16" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
@@ -9777,7 +9726,7 @@
       <c r="N16" s="35"/>
       <c r="O16" s="35"/>
     </row>
-    <row r="17" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="118" t="s">
         <v>1</v>
       </c>
@@ -9787,7 +9736,7 @@
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
     </row>
-    <row r="18" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="str">
         <f>HYPERLINK("#'Constants - Rice cultivation'!A1", "Constants - Rice cultivation")</f>
         <v>Constants - Rice cultivation</v>
@@ -9798,7 +9747,7 @@
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
     </row>
-    <row r="19" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
@@ -9810,7 +9759,7 @@
       <c r="H19" s="1"/>
       <c r="N19" s="37"/>
     </row>
-    <row r="20" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
@@ -9819,7 +9768,7 @@
       <c r="H20" s="1"/>
       <c r="N20" s="38"/>
     </row>
-    <row r="21" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
@@ -9827,7 +9776,7 @@
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
     </row>
-    <row r="22" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
@@ -9835,7 +9784,7 @@
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
     </row>
-    <row r="23" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
@@ -9843,7 +9792,7 @@
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
     </row>
-    <row r="24" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
@@ -9851,7 +9800,7 @@
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
     </row>
-    <row r="25" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
@@ -9860,7 +9809,7 @@
       <c r="H25" s="1"/>
       <c r="N25" s="38"/>
     </row>
-    <row r="26" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
@@ -9868,7 +9817,7 @@
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
     </row>
-    <row r="27" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
@@ -9876,7 +9825,7 @@
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
     </row>
-    <row r="28" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
@@ -9884,7 +9833,7 @@
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
     </row>
-    <row r="29" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
@@ -9892,7 +9841,7 @@
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
     </row>
-    <row r="30" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
@@ -9914,7 +9863,7 @@
       <c r="X30" s="43"/>
       <c r="Y30" s="43"/>
     </row>
-    <row r="31" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
@@ -9936,7 +9885,7 @@
       <c r="X31" s="42"/>
       <c r="Y31" s="42"/>
     </row>
-    <row r="32" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
@@ -9958,7 +9907,7 @@
       <c r="X32" s="42"/>
       <c r="Y32" s="42"/>
     </row>
-    <row r="33" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
@@ -9980,7 +9929,7 @@
       <c r="X33" s="42"/>
       <c r="Y33" s="42"/>
     </row>
-    <row r="34" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
@@ -10004,7 +9953,7 @@
       <c r="X34" s="42"/>
       <c r="Y34" s="42"/>
     </row>
-    <row r="35" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
@@ -10028,7 +9977,7 @@
       <c r="X35" s="42"/>
       <c r="Y35" s="42"/>
     </row>
-    <row r="36" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
@@ -10053,7 +10002,7 @@
       <c r="X36" s="42"/>
       <c r="Y36" s="42"/>
     </row>
-    <row r="37" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37"/>
       <c r="D37" s="59"/>
       <c r="E37" s="59"/>
@@ -10078,7 +10027,7 @@
       <c r="X37" s="42"/>
       <c r="Y37" s="42"/>
     </row>
-    <row r="38" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38"/>
       <c r="D38" s="59"/>
       <c r="E38" s="59"/>
@@ -10103,7 +10052,7 @@
       <c r="X38" s="42"/>
       <c r="Y38" s="42"/>
     </row>
-    <row r="39" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39"/>
       <c r="D39" s="59"/>
       <c r="E39" s="59"/>
@@ -10128,7 +10077,7 @@
       <c r="X39" s="42"/>
       <c r="Y39" s="42"/>
     </row>
-    <row r="40" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40"/>
       <c r="D40" s="62"/>
       <c r="E40" s="62"/>
@@ -10153,27 +10102,27 @@
       <c r="X40" s="44"/>
       <c r="Y40" s="44"/>
     </row>
-    <row r="41" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41"/>
     </row>
-    <row r="42" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42"/>
     </row>
-    <row r="43" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43"/>
     </row>
-    <row r="44" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44"/>
     </row>
-    <row r="45" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45"/>
       <c r="D45" s="6"/>
     </row>
-    <row r="46" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46"/>
       <c r="D46" s="6"/>
     </row>
-    <row r="47" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47"/>
       <c r="D47" s="65"/>
       <c r="E47" s="65"/>
@@ -10181,7 +10130,7 @@
       <c r="G47" s="65"/>
       <c r="H47" s="65"/>
     </row>
-    <row r="48" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48"/>
       <c r="D48" s="31"/>
       <c r="E48" s="31"/>
@@ -10189,7 +10138,7 @@
       <c r="G48" s="32"/>
       <c r="H48" s="31"/>
     </row>
-    <row r="49" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49"/>
       <c r="D49" s="31"/>
       <c r="E49" s="31"/>
@@ -10197,7 +10146,7 @@
       <c r="G49" s="32"/>
       <c r="H49" s="31"/>
     </row>
-    <row r="50" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50"/>
       <c r="D50" s="31"/>
       <c r="E50" s="31"/>
@@ -10205,7 +10154,7 @@
       <c r="G50" s="32"/>
       <c r="H50" s="31"/>
     </row>
-    <row r="51" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51"/>
       <c r="D51" s="66"/>
       <c r="E51" s="67"/>
@@ -10213,76 +10162,76 @@
       <c r="G51" s="67"/>
       <c r="H51" s="68"/>
     </row>
-    <row r="52" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52"/>
     </row>
-    <row r="53" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53"/>
     </row>
-    <row r="54" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54"/>
       <c r="G54" s="69"/>
     </row>
-    <row r="55" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55"/>
       <c r="D55" s="6"/>
     </row>
-    <row r="56" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56"/>
     </row>
-    <row r="57" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57"/>
       <c r="D57" s="20"/>
       <c r="F57" s="70"/>
     </row>
-    <row r="58" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58"/>
       <c r="D58" s="1"/>
       <c r="E58" s="71"/>
     </row>
-    <row r="59" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59"/>
       <c r="D59" s="1"/>
       <c r="E59" s="71"/>
     </row>
-    <row r="60" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60"/>
       <c r="D60" s="1"/>
       <c r="E60" s="72"/>
     </row>
-    <row r="61" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61"/>
       <c r="D61" s="1"/>
     </row>
-    <row r="62" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62"/>
     </row>
-    <row r="63" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63"/>
       <c r="D63" s="20"/>
     </row>
-    <row r="64" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64"/>
       <c r="D64" s="1"/>
       <c r="E64" s="71"/>
     </row>
-    <row r="65" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65"/>
       <c r="D65" s="1"/>
       <c r="E65" s="71"/>
     </row>
-    <row r="66" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66"/>
       <c r="D66" s="1"/>
       <c r="E66" s="72"/>
     </row>
-    <row r="67" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67"/>
     </row>
-    <row r="68" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68"/>
     </row>
-    <row r="69" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69"/>
       <c r="D69" s="52"/>
       <c r="E69" s="52"/>
@@ -10291,7 +10240,7 @@
       <c r="H69" s="52"/>
       <c r="I69" s="52"/>
     </row>
-    <row r="70" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70"/>
       <c r="D70" s="52"/>
       <c r="E70" s="52"/>
@@ -10300,7 +10249,7 @@
       <c r="H70" s="52"/>
       <c r="I70" s="52"/>
     </row>
-    <row r="71" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71"/>
       <c r="D71" s="52"/>
       <c r="E71" s="52"/>
@@ -10309,7 +10258,7 @@
       <c r="H71" s="52"/>
       <c r="I71" s="52"/>
     </row>
-    <row r="72" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72"/>
       <c r="D72" s="52"/>
       <c r="E72" s="52"/>
@@ -10318,273 +10267,273 @@
       <c r="H72" s="52"/>
       <c r="I72" s="52"/>
     </row>
-    <row r="73" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73"/>
     </row>
-    <row r="74" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74"/>
     </row>
-    <row r="75" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75"/>
     </row>
-    <row r="76" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76"/>
     </row>
-    <row r="77" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77"/>
     </row>
-    <row r="78" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78"/>
       <c r="D78" s="73"/>
     </row>
-    <row r="79" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79"/>
       <c r="D79" s="73"/>
     </row>
-    <row r="80" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80"/>
       <c r="D80" s="73"/>
     </row>
-    <row r="81" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81"/>
       <c r="D81" s="73"/>
     </row>
-    <row r="82" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82"/>
       <c r="D82" s="73"/>
     </row>
-    <row r="83" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83"/>
     </row>
-    <row r="84" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84"/>
     </row>
-    <row r="85" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85"/>
     </row>
-    <row r="86" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86"/>
     </row>
-    <row r="87" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87"/>
     </row>
-    <row r="88" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88"/>
     </row>
-    <row r="89" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89"/>
     </row>
-    <row r="90" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90"/>
     </row>
-    <row r="91" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91"/>
     </row>
-    <row r="92" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92"/>
     </row>
-    <row r="93" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93"/>
     </row>
-    <row r="94" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94"/>
     </row>
-    <row r="95" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95"/>
     </row>
-    <row r="96" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96"/>
     </row>
-    <row r="97" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97"/>
     </row>
-    <row r="98" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98"/>
     </row>
-    <row r="99" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99"/>
     </row>
-    <row r="100" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100"/>
     </row>
-    <row r="101" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101"/>
     </row>
-    <row r="102" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102"/>
     </row>
-    <row r="103" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103"/>
     </row>
-    <row r="104" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104"/>
     </row>
-    <row r="105" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105"/>
     </row>
-    <row r="106" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106"/>
     </row>
-    <row r="107" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107"/>
     </row>
-    <row r="108" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108"/>
     </row>
-    <row r="109" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109"/>
     </row>
-    <row r="110" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110"/>
     </row>
-    <row r="111" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111"/>
     </row>
-    <row r="112" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112"/>
     </row>
-    <row r="113" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113"/>
     </row>
-    <row r="114" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114"/>
     </row>
-    <row r="115" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115"/>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A116"/>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A117"/>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A118"/>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A119"/>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A120"/>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A121"/>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A122"/>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A123"/>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A124"/>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A125"/>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A126"/>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A127"/>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A128"/>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A129"/>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A130"/>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A131"/>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A132"/>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A133"/>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A134"/>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A135"/>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A136"/>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A137"/>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A138"/>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A139"/>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A140"/>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A141"/>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A142"/>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A143"/>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A144"/>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A145"/>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A146"/>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A147"/>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A148"/>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A149"/>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A150"/>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A151"/>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A152"/>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A153"/>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A154"/>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A155"/>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A156"/>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A157"/>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A158"/>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A159"/>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A160"/>
     </row>
   </sheetData>
@@ -10613,7 +10562,7 @@
     <tabColor theme="5" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:K363"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -10632,10 +10581,10 @@
         <v>106</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="9" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" s="9" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2"/>
     </row>
-    <row r="3" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -10650,13 +10599,13 @@
       <c r="J3" s="15"/>
       <c r="K3" s="15"/>
     </row>
-    <row r="4" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="str">
         <f>HYPERLINK("#'Overview'!A1", "Overview")</f>
         <v>Overview</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
@@ -10665,8 +10614,8 @@
         <v>103</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D7" s="80" t="s">
         <v>104</v>
       </c>
@@ -10674,18 +10623,18 @@
       <c r="F7" s="81"/>
       <c r="G7" s="76"/>
     </row>
-    <row r="8" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="str">
         <f>HYPERLINK("#'Input - Site'!A1", "Site")</f>
         <v>Site</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="97" t="str">
         <f>HYPERLINK("#'Input - Rice'!A1", "Rice")</f>
         <v>Rice</v>
@@ -10701,18 +10650,18 @@
         <v>151</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D12" s="6" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="str">
         <f>HYPERLINK("#'7.1.1-2 Rice cultivation'!A1", "7.1.1-2 Rice cultivation")</f>
         <v>7.1.1-2 Rice cultivation</v>
@@ -10739,7 +10688,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D15" s="34" t="s">
         <v>152</v>
       </c>
@@ -10762,7 +10711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D16" s="34" t="s">
         <v>153</v>
       </c>
@@ -10785,18 +10734,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="118" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="str">
         <f>HYPERLINK("#'Constants - Rice cultivation'!A1", "Constants - Rice cultivation")</f>
         <v>Constants - Rice cultivation</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
@@ -10805,8 +10754,8 @@
         <v>107</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D21" s="99" t="s">
         <v>109</v>
       </c>
@@ -10829,7 +10778,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D22" s="34" t="s">
         <v>140</v>
       </c>
@@ -10852,7 +10801,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D23" s="34" t="s">
         <v>141</v>
       </c>
@@ -10875,27 +10824,27 @@
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C37" s="102"/>
     </row>
-    <row r="38" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C38" s="102"/>
     </row>
-    <row r="39" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="1:11" s="103" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="1:11" s="103" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40"/>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
@@ -10907,7 +10856,7 @@
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
     </row>
-    <row r="41" spans="1:11" s="103" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" s="103" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
@@ -10919,133 +10868,133 @@
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
     </row>
-    <row r="42" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D88" s="6"/>
     </row>
-    <row r="89" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="116" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="117" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="118" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="119" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="129" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="130" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="135" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="146" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="155" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="363" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" spans="4:4" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D363" s="89"/>
     </row>
   </sheetData>
@@ -11147,7 +11096,7 @@
     <tabColor rgb="FF008000"/>
   </sheetPr>
   <dimension ref="A1:V342"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -11169,11 +11118,11 @@
       </c>
       <c r="M1"/>
     </row>
-    <row r="2" spans="1:22" s="9" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" s="9" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2"/>
       <c r="M2"/>
     </row>
-    <row r="3" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -11202,13 +11151,13 @@
       <c r="U3" s="4"/>
       <c r="V3" s="4"/>
     </row>
-    <row r="4" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="str">
         <f>HYPERLINK("#'Overview'!A1", "Overview")</f>
         <v>Overview</v>
       </c>
     </row>
-    <row r="5" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
@@ -11222,7 +11171,7 @@
       <c r="G5" s="21"/>
       <c r="H5" s="21"/>
     </row>
-    <row r="6" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D6" s="5" t="str" cm="1">
         <f t="array" ref="D6">RiceCultivation_Equations.VEERG_7_1_1_1__3_OrganicAmendmentsScalingFactor_Source()</f>
         <v>VEERG 2026: 7.1.1.1, Equation (3)</v>
@@ -11233,14 +11182,14 @@
       <c r="H6" s="21"/>
       <c r="L6" s="21"/>
     </row>
-    <row r="7" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D7" s="49" t="str" cm="1">
         <f t="array" ref="D7:D10">RiceCultivation_Equations.VEERG_7_1_1_1__3_OrganicAmendmentsScalingFactor_Variation()</f>
         <v>VARIATION ON SOURCE:</v>
       </c>
       <c r="L7" s="21"/>
     </row>
-    <row r="8" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
         <v>0</v>
       </c>
@@ -11249,7 +11198,7 @@
       </c>
       <c r="L8" s="21"/>
     </row>
-    <row r="9" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="str">
         <f>HYPERLINK("#'Input - Site'!A1", "Site")</f>
         <v>Site</v>
@@ -11259,7 +11208,7 @@
       </c>
       <c r="L9" s="21"/>
     </row>
-    <row r="10" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="str">
         <f>HYPERLINK("#'Input - Rice'!A1", "Rice")</f>
         <v>Rice</v>
@@ -11268,7 +11217,7 @@
         <v>Declared each amendment separately to allow summing in Excel in one equation</v>
       </c>
     </row>
-    <row r="11" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D11" s="13" t="s">
         <v>13</v>
       </c>
@@ -11281,13 +11230,13 @@
       <c r="H11" s="21"/>
       <c r="L11" s="21"/>
     </row>
-    <row r="12" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F12" s="5"/>
       <c r="G12" s="21"/>
       <c r="H12" s="21"/>
       <c r="L12" s="21"/>
     </row>
-    <row r="13" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>51</v>
       </c>
@@ -11298,7 +11247,7 @@
       <c r="H13" s="21"/>
       <c r="L13" s="21"/>
     </row>
-    <row r="14" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="116" t="str">
         <f>HYPERLINK("#'7.1.1-2 Rice cultivation'!A1", "7.1.1-2 Rice cultivation")</f>
         <v>7.1.1-2 Rice cultivation</v>
@@ -11315,7 +11264,7 @@
       <c r="H14" s="21"/>
       <c r="L14" s="21"/>
     </row>
-    <row r="15" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D15" s="47" t="s">
         <v>8</v>
       </c>
@@ -11328,13 +11277,13 @@
       <c r="H15" s="21"/>
       <c r="L15" s="21"/>
     </row>
-    <row r="16" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D16" s="21"/>
       <c r="E16" s="21"/>
       <c r="F16" s="21"/>
       <c r="G16" s="21"/>
     </row>
-    <row r="17" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="118" t="s">
         <v>1</v>
       </c>
@@ -11358,7 +11307,7 @@
         <v>Table_ROA_o</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="str">
         <f>HYPERLINK("#'Constants - Rice cultivation'!A1", "Constants - Rice cultivation")</f>
         <v>Constants - Rice cultivation</v>
@@ -11381,7 +11330,7 @@
         <v>Table_CFOA_o</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
@@ -11404,14 +11353,14 @@
         <v>Table_ROA_o</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D20" s="21"/>
       <c r="E20" s="21"/>
       <c r="F20" s="21"/>
       <c r="G20" s="21"/>
       <c r="H20" s="21"/>
     </row>
-    <row r="21" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D21" s="83" t="s">
         <v>136</v>
       </c>
@@ -11419,7 +11368,7 @@
       <c r="F21" s="6"/>
       <c r="G21" s="21"/>
     </row>
-    <row r="22" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D22" s="82" t="s">
         <v>112</v>
       </c>
@@ -11428,7 +11377,7 @@
       <c r="G22" s="21"/>
       <c r="H22" s="21"/>
     </row>
-    <row r="23" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D23" s="99" t="s">
         <v>130</v>
       </c>
@@ -11456,7 +11405,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D24" s="46" t="str" cm="1">
         <f t="array" ref="D24:D28">IFERROR(INDEX(Table_Input_AmendmentBlends[Amendment mix name], _xlfn.SEQUENCE(5)), "")</f>
         <v>Mix 1</v>
@@ -11490,7 +11439,7 @@
         <v>tonnes/ha</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D25" s="46" t="str">
         <v>Mix 2</v>
       </c>
@@ -11513,7 +11462,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D26" s="46" t="str">
         <v/>
       </c>
@@ -11536,7 +11485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D27" s="46" t="str">
         <v/>
       </c>
@@ -11559,7 +11508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D28" s="46" t="str">
         <v/>
       </c>
@@ -11582,18 +11531,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D30" s="83" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D31" s="82" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D32" s="45" t="s">
         <v>134</v>
       </c>
@@ -11601,7 +11550,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="33" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D33" s="46" t="str">
         <f>'Constants - Rice cultivation'!D39</f>
         <v>Straw incorporated shortly (&lt;30 days) before cultivation</v>
@@ -11615,7 +11564,7 @@
         <v>fraction</v>
       </c>
     </row>
-    <row r="34" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D34" s="46" t="str">
         <f>'Constants - Rice cultivation'!D40</f>
         <v>Straw incorporated long (&gt;30 days) before cultivation</v>
@@ -11625,7 +11574,7 @@
         <v>0.19</v>
       </c>
     </row>
-    <row r="35" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D35" s="46" t="str">
         <f>'Constants - Rice cultivation'!D41</f>
         <v>Compost</v>
@@ -11635,7 +11584,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="36" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D36" s="46" t="str">
         <f>'Constants - Rice cultivation'!D42</f>
         <v>Farm yard manure</v>
@@ -11645,7 +11594,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="37" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D37" s="46" t="str">
         <f>'Constants - Rice cultivation'!D43</f>
         <v>Green manure</v>
@@ -11655,7 +11604,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="38" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D38" s="46" t="str">
         <f>'Constants - Rice cultivation'!D44</f>
         <v>Inorganic fertiliser</v>
@@ -11665,18 +11614,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D40" s="83" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="41" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D41" s="82" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="42" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D42" s="45" t="s">
         <v>130</v>
       </c>
@@ -11684,7 +11633,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="43" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D43" s="46" t="str" cm="1">
         <f t="array" ref="D43:D47">IFERROR(INDEX(Table_Input_AmendmentBlends[Amendment mix name], _xlfn.SEQUENCE(5)), "")</f>
         <v>Mix 1</v>
@@ -11694,7 +11643,7 @@
         <v>2.3450162437672319</v>
       </c>
     </row>
-    <row r="44" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D44" s="46" t="str">
         <v>Mix 2</v>
       </c>
@@ -11703,7 +11652,7 @@
         <v>2.1982259075210928</v>
       </c>
     </row>
-    <row r="45" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D45" s="46" t="str">
         <v/>
       </c>
@@ -11712,7 +11661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D46" s="46" t="str">
         <v/>
       </c>
@@ -11721,7 +11670,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D47" s="46" t="str">
         <v/>
       </c>
@@ -11730,9 +11679,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C50" s="41"/>
       <c r="D50" s="41"/>
       <c r="E50" s="41"/>
@@ -11744,19 +11693,19 @@
       <c r="K50" s="41"/>
       <c r="L50" s="41"/>
     </row>
-    <row r="51" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D51" s="6" t="str" cm="1">
         <f t="array" ref="D51">RiceCultivation_Equations.VEERG_7_1_1_1__2_EmissionFactorForRiceCultivation_Title()</f>
         <v>Emission factor for rice cultivation</v>
       </c>
     </row>
-    <row r="52" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D52" s="5" t="str" cm="1">
         <f t="array" ref="D52">RiceCultivation_Equations.VEERG_7_1_1_1__2_EmissionFactorForRiceCultivation_Source()</f>
         <v>VEERG 2026: 7.1.1.1, Equation (2)</v>
       </c>
     </row>
-    <row r="53" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D53" s="13" t="s">
         <v>13</v>
       </c>
@@ -11765,9 +11714,9 @@
         <v>=RiceCultivation_Equations.VEERG_7_1_1_1__2_EmissionFactorForRiceCultivation</v>
       </c>
     </row>
-    <row r="54" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D56" s="47" t="s">
         <v>16</v>
       </c>
@@ -11776,7 +11725,7 @@
         <v>EF_ricewpo</v>
       </c>
     </row>
-    <row r="57" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D57" s="47" t="s">
         <v>8</v>
       </c>
@@ -11785,8 +11734,8 @@
         <v>kg CH4/ha/day</v>
       </c>
     </row>
-    <row r="58" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D59" s="106" t="str" cm="1">
         <f t="array" ref="D59:E65">_xlfn.CHOOSECOLS(RiceCultivation_Equations.VEERG_7_1_1_1__2_EmissionFactorForRiceCultivation_Arguments(),1,2)</f>
         <v>EF_c</v>
@@ -11808,7 +11757,7 @@
         <v>1.19</v>
       </c>
     </row>
-    <row r="60" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D60" s="106" t="str">
         <v>SF_w</v>
       </c>
@@ -11828,7 +11777,7 @@
         <v>Table_EF_rice_w_p_o</v>
       </c>
     </row>
-    <row r="61" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D61" s="106" t="str">
         <v>SF_p</v>
       </c>
@@ -11848,7 +11797,7 @@
         <v>Table_EF_rice_w_p_o</v>
       </c>
     </row>
-    <row r="62" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D62" s="106" t="str">
         <v>SF_o</v>
       </c>
@@ -11868,7 +11817,7 @@
         <v>Table_EF_rice_w_p_o</v>
       </c>
     </row>
-    <row r="63" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D63" s="106" t="str">
         <v>w</v>
       </c>
@@ -11889,7 +11838,7 @@
       </c>
       <c r="L63" s="21"/>
     </row>
-    <row r="64" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D64" s="106" t="str">
         <v>p</v>
       </c>
@@ -11910,7 +11859,7 @@
       </c>
       <c r="L64" s="21"/>
     </row>
-    <row r="65" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D65" s="106" t="str">
         <v>o</v>
       </c>
@@ -11930,18 +11879,18 @@
         <v>Table_EF_rice_w_p_o</v>
       </c>
     </row>
-    <row r="66" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D67" s="83" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="68" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D68" s="82" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="69" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D69" s="99" t="s">
         <v>139</v>
       </c>
@@ -11967,7 +11916,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="70" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D70" s="46" t="str" cm="1">
         <f t="array" ref="D70:D74">IFERROR(INDEX(Table_Input_Regimes[Regime name], _xlfn.SEQUENCE(5)), "")</f>
         <v>Regime 1</v>
@@ -12001,7 +11950,7 @@
         <v>0.44649109281328092</v>
       </c>
     </row>
-    <row r="71" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D71" s="46" t="str">
         <v>Regime 2</v>
       </c>
@@ -12031,7 +11980,7 @@
         <v>4.4760473769276166</v>
       </c>
     </row>
-    <row r="72" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D72" s="46" t="str">
         <v/>
       </c>
@@ -12061,7 +12010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D73" s="46" t="str">
         <v/>
       </c>
@@ -12091,7 +12040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D74" s="46" t="str">
         <v/>
       </c>
@@ -12121,9 +12070,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C77" s="41"/>
       <c r="D77" s="41"/>
       <c r="E77" s="41"/>
@@ -12135,25 +12084,25 @@
       <c r="K77" s="41"/>
       <c r="L77" s="41"/>
     </row>
-    <row r="78" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D78" s="6" t="str" cm="1">
         <f t="array" ref="D78">RiceCultivation_Equations.VEERG_7_1_1_1__1_MethaneEmissionsFromRiceCultivation_Title()</f>
         <v>Methane emissions from rice cultivation</v>
       </c>
     </row>
-    <row r="79" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D79" s="5" t="str" cm="1">
         <f t="array" ref="D79">RiceCultivation_Equations.VEERG_7_1_1_1__1_MethaneEmissionsFromRiceCultivation_Source()</f>
         <v>VEERG 2026: 7.1.1.1, Equation (1)</v>
       </c>
     </row>
-    <row r="80" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D80" s="49" t="str" cm="1">
         <f t="array" ref="D80">RiceCultivation_Equations.VEERG_7_1_1_1__1_MethaneEmissionsFromRiceCultivation_Variation()</f>
         <v>Added 'number of seasons' variable as per VEERG description in 7.2.1 'Where there is more than one cropping season per year, Arice,wpo shall be scaled accordingly'</v>
       </c>
     </row>
-    <row r="81" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D81" s="13" t="s">
         <v>13</v>
       </c>
@@ -12162,10 +12111,10 @@
         <v>=RiceCultivation_Equations.VEERG_7_1_1_1__1_MethaneEmissionsFromRiceCultivation</v>
       </c>
     </row>
-    <row r="82" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D85" s="47" t="s">
         <v>16</v>
       </c>
@@ -12174,7 +12123,7 @@
         <v>E_rice</v>
       </c>
     </row>
-    <row r="86" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D86" s="47" t="s">
         <v>8</v>
       </c>
@@ -12183,8 +12132,8 @@
         <v>t CH4</v>
       </c>
     </row>
-    <row r="87" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D88" s="106" t="str" cm="1">
         <f t="array" ref="D88:E91">_xlfn.CHOOSECOLS(RiceCultivation_Equations.VEERG_7_1_1_1__1_MethaneEmissionsFromRiceCultivation_Arguments(),1,2)</f>
         <v>A_ricewpo</v>
@@ -12206,7 +12155,7 @@
         <v>Table_E_rice</v>
       </c>
     </row>
-    <row r="89" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D89" s="106" t="str">
         <v>EF_ricewpo</v>
       </c>
@@ -12226,7 +12175,7 @@
         <v>Table_EF_rice_w_p_o</v>
       </c>
     </row>
-    <row r="90" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D90" s="106" t="str">
         <v>t_ricewpo</v>
       </c>
@@ -12246,7 +12195,7 @@
         <v>Table_E_rice</v>
       </c>
     </row>
-    <row r="91" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D91" s="106" t="str">
         <v>s</v>
       </c>
@@ -12266,18 +12215,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="92" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D93" s="83" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="94" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D94" s="82" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="95" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D95" s="99" t="s">
         <v>139</v>
       </c>
@@ -12291,7 +12240,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="96" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D96" s="46" t="str" cm="1">
         <f t="array" ref="D96:D100">IFERROR(INDEX(Table_Input_Regimes[Regime name], _xlfn.SEQUENCE(5)), "")</f>
         <v>Regime 1</v>
@@ -12313,7 +12262,7 @@
         <v>t CH4</v>
       </c>
     </row>
-    <row r="97" spans="4:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="4:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D97" s="46" t="str">
         <v>Regime 2</v>
       </c>
@@ -12328,7 +12277,7 @@
         <v>89.520947538552321</v>
       </c>
     </row>
-    <row r="98" spans="4:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="4:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D98" s="46" t="str">
         <v/>
       </c>
@@ -12343,7 +12292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="4:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="4:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D99" s="46" t="str">
         <v/>
       </c>
@@ -12358,7 +12307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="4:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="4:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D100" s="46" t="str">
         <v/>
       </c>
@@ -12373,8 +12322,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="4:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" spans="4:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="4:12" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" spans="4:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D102" s="84" t="s">
         <v>87</v>
       </c>
@@ -12387,8 +12336,8 @@
         <v>t CH4</v>
       </c>
     </row>
-    <row r="103" spans="4:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" spans="4:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="4:12" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" spans="4:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D104" s="50" t="str" cm="1">
         <f t="array" ref="D104:E105">Common_Equations.Common_ConvertCH4ToCO2e_Arguments()</f>
         <v>ECH4</v>
@@ -12402,7 +12351,7 @@
         <v>98.450769394817939</v>
       </c>
     </row>
-    <row r="105" spans="4:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="4:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D105" s="50" t="str">
         <v>GWPCH4</v>
       </c>
@@ -12415,8 +12364,8 @@
         <v>28</v>
       </c>
     </row>
-    <row r="106" spans="4:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" spans="4:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="4:12" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" spans="4:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D107" s="41" t="s">
         <v>59</v>
       </c>
@@ -12429,32 +12378,32 @@
         <v>t CO2e</v>
       </c>
     </row>
-    <row r="108" spans="4:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" spans="4:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="4:12" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" spans="4:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D109" s="21"/>
       <c r="E109" s="21"/>
       <c r="F109" s="21"/>
       <c r="G109" s="21"/>
       <c r="H109" s="21"/>
     </row>
-    <row r="110" spans="4:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" spans="4:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" spans="4:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="4:12" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" spans="4:12" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" spans="4:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H112" s="21"/>
       <c r="L112" s="21"/>
     </row>
-    <row r="113" spans="4:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="4:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L113" s="21"/>
     </row>
-    <row r="114" spans="4:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="4:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H114" s="21"/>
       <c r="L114" s="21"/>
     </row>
-    <row r="115" spans="4:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="4:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H115" s="21"/>
       <c r="L115" s="21"/>
     </row>
-    <row r="116" spans="4:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="4:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D116" s="21"/>
       <c r="E116" s="21"/>
       <c r="F116" s="94"/>
@@ -12465,167 +12414,167 @@
       <c r="K116" s="21"/>
       <c r="L116" s="21"/>
     </row>
-    <row r="117" spans="4:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="4:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L117" s="21"/>
     </row>
-    <row r="118" spans="4:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="119" spans="4:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" spans="4:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" spans="4:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" spans="4:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" spans="4:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" spans="4:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" spans="4:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" spans="4:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" spans="4:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" spans="4:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="129" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="130" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="135" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="146" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="155" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="166" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="167" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="168" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="169" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="170" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="171" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="172" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="173" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="174" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="175" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="176" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="177" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="178" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="179" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="180" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="181" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="182" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="183" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="184" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="185" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="186" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="187" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="188" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="189" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="190" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="191" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="192" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="193" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="194" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="195" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="196" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="197" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="198" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="199" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="200" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="201" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="202" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="203" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="204" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="205" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="206" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="207" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="208" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="209" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="210" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="211" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="212" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="213" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="214" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="215" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="216" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="217" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="218" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="219" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="220" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="221" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="222" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="223" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="224" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="225" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="226" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="227" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="228" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="229" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="230" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="231" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="232" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="233" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="234" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="235" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="236" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="237" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="238" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="239" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="240" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="241" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="242" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="243" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="244" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="245" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="246" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="247" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="248" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="249" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="250" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="251" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="252" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="253" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="254" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="255" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="256" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="257" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="258" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="259" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="260" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="261" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="262" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="263" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="264" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="265" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="266" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="267" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="268" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="269" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="270" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="271" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="341" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="4:12" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" spans="4:12" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" spans="4:12" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" spans="4:12" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" spans="4:12" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" spans="4:12" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" spans="4:12" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" spans="4:12" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" spans="4:12" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" spans="4:12" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" spans="4:12" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" spans="8:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="H341" s="21"/>
     </row>
-    <row r="342" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="342" spans="8:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="H342" s="21"/>
     </row>
   </sheetData>
@@ -12647,7 +12596,7 @@
     <tabColor theme="2" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:AI165"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -12671,13 +12620,13 @@
       <c r="AH1"/>
       <c r="AI1"/>
     </row>
-    <row r="2" spans="1:35" s="9" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:35" s="9" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2"/>
       <c r="AG2"/>
       <c r="AH2"/>
       <c r="AI2"/>
     </row>
-    <row r="3" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -12713,13 +12662,13 @@
       <c r="AE3" s="4"/>
       <c r="AF3" s="4"/>
     </row>
-    <row r="4" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="str">
         <f>HYPERLINK("#'Overview'!A1", "Overview")</f>
         <v>Overview</v>
       </c>
     </row>
-    <row r="5" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
@@ -12729,13 +12678,13 @@
         <v>Scaling factor based on the water regime employed during the growing season cultivation period</v>
       </c>
     </row>
-    <row r="6" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D6" s="5" t="str" cm="1">
         <f t="array" ref="D6">RiceCultivation_SourceData.SourceData_RiceCultivation_WaterScalingFactorGrowingSeason_Source()</f>
         <v>VEERG 2026: Table A.2.3.1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D7" s="1" t="str" cm="1">
         <f t="array" ref="D7">RiceCultivation_SourceData.SourceData_RiceCultivation_WaterScalingFactorGrowingSeason_Variable()</f>
         <v>SFw</v>
@@ -12744,7 +12693,7 @@
       <c r="AH7" s="1"/>
       <c r="AI7" s="1"/>
     </row>
-    <row r="8" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
         <v>0</v>
       </c>
@@ -12765,7 +12714,7 @@
       <c r="AH8" s="1"/>
       <c r="AI8" s="1"/>
     </row>
-    <row r="9" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="str">
         <f>HYPERLINK("#'Input - Site'!A1", "Site")</f>
         <v>Site</v>
@@ -12792,7 +12741,7 @@
       <c r="AH9" s="1"/>
       <c r="AI9" s="1"/>
     </row>
-    <row r="10" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="str">
         <f>HYPERLINK("#'Input - Rice'!A1", "Rice")</f>
         <v>Rice</v>
@@ -12825,7 +12774,7 @@
       <c r="AH10" s="1"/>
       <c r="AI10" s="1"/>
     </row>
-    <row r="11" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D11" s="1" t="str" cm="1">
         <f t="array" ref="D11">Common_InputFunctions.Utility_DisplayArrayInTable(RiceCultivation_SourceData.SourceData_RiceCultivation_WaterScalingFactorGrowingSeason_Data(),Table_SourceData_WaterScalingFactorGrowingSeason[[#Headers],[Water regime type]],0)</f>
         <v>Upland</v>
@@ -12851,7 +12800,7 @@
         <v>Drought prone</v>
       </c>
     </row>
-    <row r="12" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D12" s="1" t="str" cm="1">
         <f t="array" ref="D12">Common_InputFunctions.Utility_DisplayArrayInTable(RiceCultivation_SourceData.SourceData_RiceCultivation_WaterScalingFactorGrowingSeason_Data(),Table_SourceData_WaterScalingFactorGrowingSeason[[#Headers],[Water regime type]],0)</f>
         <v>Irrigated</v>
@@ -12873,7 +12822,7 @@
         <v>Deep water</v>
       </c>
     </row>
-    <row r="13" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>51</v>
       </c>
@@ -12890,7 +12839,7 @@
         <v>0.71</v>
       </c>
     </row>
-    <row r="14" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="str">
         <f>HYPERLINK("#'7.1.1-2 Rice cultivation'!A1", "7.1.1-2 Rice cultivation")</f>
         <v>7.1.1-2 Rice cultivation</v>
@@ -12908,7 +12857,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="15" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D15" s="1" t="str" cm="1">
         <f t="array" ref="D15">Common_InputFunctions.Utility_DisplayArrayInTable(RiceCultivation_SourceData.SourceData_RiceCultivation_WaterScalingFactorGrowingSeason_Data(),Table_SourceData_WaterScalingFactorGrowingSeason[[#Headers],[Water regime type]],0)</f>
         <v>Rainfed and deep water</v>
@@ -12922,7 +12871,7 @@
         <v>0.54</v>
       </c>
     </row>
-    <row r="16" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D16" s="1" t="str" cm="1">
         <f t="array" ref="D16">Common_InputFunctions.Utility_DisplayArrayInTable(RiceCultivation_SourceData.SourceData_RiceCultivation_WaterScalingFactorGrowingSeason_Data(),Table_SourceData_WaterScalingFactorGrowingSeason[[#Headers],[Water regime type]],0)</f>
         <v>Rainfed and deep water</v>
@@ -12936,7 +12885,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="118" t="s">
         <v>1</v>
       </c>
@@ -12953,43 +12902,43 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="117" t="str">
         <f>HYPERLINK("#'Constants - Rice cultivation'!A1", "Constants - Rice cultivation")</f>
         <v>Constants - Rice cultivation</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D20" s="6" t="str" cm="1">
         <f t="array" ref="D20">RiceCultivation_SourceData.SourceData_RiceCultivation_WaterScalingFactorPreSeason_Title()</f>
         <v>Scaling factor based on the water regime employed in the pre - season before the growing period</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D21" s="5" t="str" cm="1">
         <f t="array" ref="D21">RiceCultivation_SourceData.SourceData_RiceCultivation_WaterScalingFactorPreSeason_Source()</f>
         <v>VEERG 2026: Table A.2.3.2</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D22" s="1" t="str" cm="1">
         <f t="array" ref="D22">RiceCultivation_SourceData.SourceData_RiceCultivation_WaterScalingFactorPreSeason_Variable()</f>
         <v>SFp</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D23" s="48" t="str" cm="1">
         <f t="array" ref="D23">RiceCultivation_SourceData.SourceData_RiceCultivation_WaterScalingFactorPreSeason_Unit()</f>
         <v>fraction</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D24" s="34" t="s">
         <v>125</v>
       </c>
@@ -12997,7 +12946,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D25" s="34" t="str" cm="1">
         <f t="array" ref="D25">Common_InputFunctions.Utility_DisplayArrayInTable(RiceCultivation_SourceData.SourceData_RiceCultivation_WaterScalingFactorPreSeason_Data(),Table_SourceData_WaterScalingFactorPreSeason[[#Headers],[Water regime prior to cultivation]], 0)</f>
         <v>Non flooded pre-season &lt;180 days</v>
@@ -13007,7 +12956,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D26" s="1" t="str" cm="1">
         <f t="array" ref="D26">Common_InputFunctions.Utility_DisplayArrayInTable(RiceCultivation_SourceData.SourceData_RiceCultivation_WaterScalingFactorPreSeason_Data(),Table_SourceData_WaterScalingFactorPreSeason[[#Headers],[Water regime prior to cultivation]], 0)</f>
         <v>Non flooded pre-season &gt;180 days</v>
@@ -13017,7 +12966,7 @@
         <v>0.89</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D27" s="1" t="str" cm="1">
         <f t="array" ref="D27">Common_InputFunctions.Utility_DisplayArrayInTable(RiceCultivation_SourceData.SourceData_RiceCultivation_WaterScalingFactorPreSeason_Data(),Table_SourceData_WaterScalingFactorPreSeason[[#Headers],[Water regime prior to cultivation]], 0)</f>
         <v>Flooded pre-season &gt;30 days</v>
@@ -13027,7 +12976,7 @@
         <v>2.41</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D28" s="1" t="str" cm="1">
         <f t="array" ref="D28">Common_InputFunctions.Utility_DisplayArrayInTable(RiceCultivation_SourceData.SourceData_RiceCultivation_WaterScalingFactorPreSeason_Data(),Table_SourceData_WaterScalingFactorPreSeason[[#Headers],[Water regime prior to cultivation]], 0)</f>
         <v>Non-flooded pre-season &gt;365 days</v>
@@ -13037,49 +12986,49 @@
         <v>0.59</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D31" s="6" t="str" cm="1">
         <f t="array" ref="D31">RiceCultivation_SourceData.SourceData_RiceCultivation_OrganicAmendmentConversionFactor_Title()</f>
         <v>Conversion factor for organic amendment i</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D32" s="5" t="str" cm="1">
         <f t="array" ref="D32">RiceCultivation_SourceData.SourceData_RiceCultivation_OrganicAmendmentConversionFactor_Source()</f>
         <v>VEERG 2026: Table A.2.3.3</v>
       </c>
     </row>
-    <row r="33" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D33" s="49" t="str" cm="1">
         <f t="array" ref="D33:D35">RiceCultivation_SourceData.SourceData_RiceCultivation_OrganicAmendmentConversionFactor_Variation()</f>
         <v>VARIATION ON SOURCE:</v>
       </c>
     </row>
-    <row r="34" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D34" s="49" t="str">
         <v>Included inorganic fertiliser as amendment as per VEERG equation description:</v>
       </c>
     </row>
-    <row r="35" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D35" s="49" t="str">
         <v>Where inorganic fertiliser is applied to the rice fields rather than organic amendments, SF_o is set to 1.</v>
       </c>
     </row>
-    <row r="36" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D36" s="1" t="str" cm="1">
         <f t="array" ref="D36">RiceCultivation_SourceData.SourceData_RiceCultivation_OrganicAmendmentConversionFactor_Variable()</f>
         <v>CFOAi</v>
       </c>
     </row>
-    <row r="37" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D37" s="48" t="str" cm="1">
         <f t="array" ref="D37">RiceCultivation_SourceData.SourceData_RiceCultivation_OrganicAmendmentConversionFactor_Unit()</f>
         <v>fraction</v>
       </c>
     </row>
-    <row r="38" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D38" s="34" t="s">
         <v>127</v>
       </c>
@@ -13087,7 +13036,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="39" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D39" s="34" t="str" cm="1">
         <f t="array" ref="D39">Common_InputFunctions.Utility_DisplayArrayInTable(RiceCultivation_SourceData.SourceData_RiceCultivation_OrganicAmendmentConversionFactor_Data(),Table15[[#Headers],[Organic amendment i]],0)</f>
         <v>Straw incorporated shortly (&lt;30 days) before cultivation</v>
@@ -13097,7 +13046,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D40" s="1" t="str" cm="1">
         <f t="array" ref="D40">Common_InputFunctions.Utility_DisplayArrayInTable(RiceCultivation_SourceData.SourceData_RiceCultivation_OrganicAmendmentConversionFactor_Data(),Table15[[#Headers],[Organic amendment i]],0)</f>
         <v>Straw incorporated long (&gt;30 days) before cultivation</v>
@@ -13107,7 +13056,7 @@
         <v>0.19</v>
       </c>
     </row>
-    <row r="41" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D41" s="1" t="str" cm="1">
         <f t="array" ref="D41">Common_InputFunctions.Utility_DisplayArrayInTable(RiceCultivation_SourceData.SourceData_RiceCultivation_OrganicAmendmentConversionFactor_Data(),Table15[[#Headers],[Organic amendment i]],0)</f>
         <v>Compost</v>
@@ -13117,7 +13066,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="42" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D42" s="1" t="str" cm="1">
         <f t="array" ref="D42">Common_InputFunctions.Utility_DisplayArrayInTable(RiceCultivation_SourceData.SourceData_RiceCultivation_OrganicAmendmentConversionFactor_Data(),Table15[[#Headers],[Organic amendment i]],0)</f>
         <v>Farm yard manure</v>
@@ -13127,7 +13076,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="43" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D43" s="1" t="str" cm="1">
         <f t="array" ref="D43">Common_InputFunctions.Utility_DisplayArrayInTable(RiceCultivation_SourceData.SourceData_RiceCultivation_OrganicAmendmentConversionFactor_Data(),Table15[[#Headers],[Organic amendment i]],0)</f>
         <v>Green manure</v>
@@ -13137,7 +13086,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="44" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D44" s="1" t="str" cm="1">
         <f t="array" ref="D44">Common_InputFunctions.Utility_DisplayArrayInTable(RiceCultivation_SourceData.SourceData_RiceCultivation_OrganicAmendmentConversionFactor_Data(),Table15[[#Headers],[Organic amendment i]],0)</f>
         <v>Inorganic fertiliser</v>
@@ -13147,21 +13096,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D47" s="6" t="str" cm="1">
         <f t="array" ref="D47">RiceCultivation_SourceData.SourceData_RiceCultivation_BaselineEF_Title()</f>
         <v>Baseline emission factor for continuously flooded fields without organic amendments</v>
       </c>
     </row>
-    <row r="48" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D48" s="5" t="str" cm="1">
         <f t="array" ref="D48">RiceCultivation_SourceData.SourceData_RiceCultivation_BaselineEF_Source()</f>
         <v>VEERG 2026: 7.2.3 Constant Parameters</v>
       </c>
     </row>
-    <row r="49" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D49" s="47" t="str" cm="1">
         <f t="array" ref="D49">RiceCultivation_SourceData.SourceData_RiceCultivation_BaselineEF_Variable()</f>
         <v>EFc</v>
@@ -13175,122 +13124,122 @@
         <v>kg CH4 / ha / day</v>
       </c>
     </row>
-    <row r="50" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="116" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="117" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="118" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="119" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="129" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="130" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="135" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="146" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="155" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="23" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13312,7 +13261,7 @@
     <tabColor theme="2" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:BY297"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="7" customWidth="1"/>
     <col min="2" max="2" width="2.7109375" style="7" customWidth="1"/>
@@ -13345,10 +13294,10 @@
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:65" s="9" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:65" s="9" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2"/>
     </row>
-    <row r="3" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -13375,11 +13324,11 @@
       <c r="V3" s="11"/>
       <c r="W3" s="11"/>
     </row>
-    <row r="4" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4"/>
       <c r="BM4" s="3"/>
     </row>
-    <row r="5" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5"/>
       <c r="D5" s="6" t="str" cm="1">
         <f t="array" ref="D5">Common_SourceData.Common_SourceData_AustralianStatesTerritories_Title()</f>
@@ -13387,7 +13336,7 @@
       </c>
       <c r="BM5" s="3"/>
     </row>
-    <row r="6" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="118" t="s">
         <v>1</v>
       </c>
@@ -13401,7 +13350,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="117" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
@@ -13419,7 +13368,7 @@
         <v>NSW</v>
       </c>
     </row>
-    <row r="8" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="str">
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
@@ -13437,7 +13386,7 @@
         <v>ACT</v>
       </c>
     </row>
-    <row r="9" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9"/>
       <c r="D9" s="34" t="str" cm="1">
         <f t="array" ref="D9">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -13452,7 +13401,7 @@
         <v>VIC</v>
       </c>
     </row>
-    <row r="10" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10"/>
       <c r="D10" s="34" t="str" cm="1">
         <f t="array" ref="D10">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -13467,7 +13416,7 @@
         <v>QLD</v>
       </c>
     </row>
-    <row r="11" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11"/>
       <c r="D11" s="34" t="str" cm="1">
         <f t="array" ref="D11">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -13483,7 +13432,7 @@
       </c>
       <c r="BM11" s="3"/>
     </row>
-    <row r="12" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12"/>
       <c r="D12" s="34" t="str" cm="1">
         <f t="array" ref="D12">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -13499,7 +13448,7 @@
       </c>
       <c r="BM12" s="3"/>
     </row>
-    <row r="13" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13"/>
       <c r="D13" s="34" t="str" cm="1">
         <f t="array" ref="D13">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -13514,7 +13463,7 @@
         <v>TAS</v>
       </c>
     </row>
-    <row r="14" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14"/>
       <c r="D14" s="34" t="str" cm="1">
         <f t="array" ref="D14">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -13529,129 +13478,129 @@
         <v>NT</v>
       </c>
     </row>
-    <row r="15" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15"/>
     </row>
-    <row r="16" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16"/>
     </row>
-    <row r="17" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17"/>
     </row>
-    <row r="18" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18"/>
       <c r="D18" s="6" t="str" cm="1">
         <f t="array" ref="D18">Common_SourceData.Common_SourceData_WASA4Areas_Title()</f>
         <v>ABS Statistcal Areas Level 4 - Western Australia</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19"/>
       <c r="D19" s="5" t="str" cm="1">
         <f t="array" ref="D19">Common_SourceData.Common_SourceData_WASA4Areas_Source()</f>
         <v>Australian Bureau of Statistics (ABS) - Statistical Areas Level 2 - 2021 - Shapefile</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20"/>
       <c r="D20" s="34" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21"/>
       <c r="D21" s="34" t="str" cm="1">
         <f t="array" ref="D21">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Bunbury</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22"/>
       <c r="D22" s="34" t="str" cm="1">
         <f t="array" ref="D22">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Mandurah</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23"/>
       <c r="D23" s="34" t="str" cm="1">
         <f t="array" ref="D23">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - Inner</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24"/>
       <c r="D24" s="34" t="str" cm="1">
         <f t="array" ref="D24">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - North East</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25"/>
       <c r="D25" s="34" t="str" cm="1">
         <f t="array" ref="D25">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - North West</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26"/>
       <c r="D26" s="34" t="str" cm="1">
         <f t="array" ref="D26">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - South East</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27"/>
       <c r="D27" s="34" t="str" cm="1">
         <f t="array" ref="D27">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - South West</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28"/>
       <c r="D28" s="34" t="str" cm="1">
         <f t="array" ref="D28">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Western Australia - Wheat Belt</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29"/>
       <c r="D29" s="34" t="str" cm="1">
         <f t="array" ref="D29">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Western Australia - Outback (North)</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30"/>
       <c r="D30" s="34" t="str" cm="1">
         <f t="array" ref="D30">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Western Australia - Outback (South)</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31"/>
     </row>
-    <row r="32" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32"/>
     </row>
-    <row r="33" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33"/>
     </row>
-    <row r="34" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34"/>
       <c r="D34" s="6" t="str" cm="1">
         <f t="array" ref="D34">Common_SourceData.Common_SourceData_GWP_Title()</f>
         <v>Global warming potential for greenhouse gases</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35"/>
       <c r="D35" s="5" t="str" cm="1">
         <f t="array" ref="D35">Common_SourceData.Common_SourceData_GWP_Source()</f>
         <v>XXXXXXX</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36"/>
       <c r="D36" s="34" t="s">
         <v>14</v>
@@ -13660,7 +13609,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37"/>
       <c r="D37" s="34" t="str" cm="1">
         <f t="array" ref="D37">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -13671,7 +13620,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38"/>
       <c r="D38" s="34" t="str" cm="1">
         <f t="array" ref="D38">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -13682,7 +13631,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39"/>
       <c r="D39" s="34" t="str" cm="1">
         <f t="array" ref="D39">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -13693,7 +13642,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40"/>
       <c r="D40" s="34" t="str" cm="1">
         <f t="array" ref="D40">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -13704,7 +13653,7 @@
         <v>6630</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41"/>
       <c r="D41" s="34" t="str" cm="1">
         <f t="array" ref="D41">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -13715,7 +13664,7 @@
         <v>12200</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42"/>
       <c r="D42" s="34" t="str" cm="1">
         <f t="array" ref="D42">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -13726,7 +13675,7 @@
         <v>22800</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43"/>
       <c r="D43" s="34" t="str" cm="1">
         <f t="array" ref="D43">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -13737,24 +13686,24 @@
         <v>17200</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44"/>
     </row>
-    <row r="45" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45"/>
       <c r="D45" s="6" t="str" cm="1">
         <f t="array" ref="D45">Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Title()</f>
         <v>Factor to convert elemental mass of gas to molecular mass</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46"/>
       <c r="D46" s="5" t="str" cm="1">
         <f t="array" ref="D46">Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Source()</f>
         <v>XXXXXXX</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47"/>
       <c r="D47" s="34" t="s">
         <v>14</v>
@@ -13772,7 +13721,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48"/>
       <c r="D48" s="34" t="str" cm="1">
         <f t="array" ref="D48">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -13795,7 +13744,7 @@
         <v>3.6666666666666665</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49"/>
       <c r="D49" s="34" t="str" cm="1">
         <f t="array" ref="D49">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -13818,7 +13767,7 @@
         <v>1.3333333333333333</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50"/>
       <c r="D50" s="34" t="str" cm="1">
         <f t="array" ref="D50">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -13841,7 +13790,7 @@
         <v>1.5714285714285714</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51"/>
       <c r="D51" s="34" t="str" cm="1">
         <f t="array" ref="D51">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -13864,7 +13813,7 @@
         <v>3.2857142857142856</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52"/>
       <c r="D52" s="34" t="str" cm="1">
         <f t="array" ref="D52">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -13887,7 +13836,7 @@
         <v>2.3333333333333335</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53"/>
       <c r="D53" s="34" t="str" cm="1">
         <f t="array" ref="D53">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -13910,7 +13859,7 @@
         <v>3.6666666666666665</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54"/>
       <c r="D54" s="34" t="str" cm="1">
         <f t="array" ref="D54">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -13933,49 +13882,49 @@
         <v>1.1666666666666667</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55"/>
     </row>
-    <row r="56" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56"/>
     </row>
-    <row r="57" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57"/>
       <c r="D57" s="6" t="str" cm="1">
         <f t="array" ref="D57">Common_SourceData.Common_SourceData_WetAndDryZones_Title()</f>
         <v>VEERG Australian wet and dry zones</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58"/>
       <c r="D58" s="5" t="str" cm="1">
         <f t="array" ref="D58">Common_SourceData.Common_SourceData_WetAndDryZones_Source()</f>
         <v>VEERG 2026: Table 1.2: Translating climate zones to wet and dry zones</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59"/>
       <c r="D59" s="49" t="str" cm="1">
         <f t="array" ref="D59:D61">"⚠️" &amp; Common_SourceData.Common_SourceData_WetAndDryZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60"/>
       <c r="D60" s="49" t="str">
         <v>⚠️Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61"/>
       <c r="D61" s="49" t="str">
         <v>⚠️Fixed typo - Changed 'Fry' to 'Dry'.</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62"/>
     </row>
-    <row r="63" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63"/>
       <c r="D63" s="34" t="s">
         <v>5</v>
@@ -13984,7 +13933,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64"/>
       <c r="D64" s="34" t="str" cm="1">
         <f t="array" ref="D64">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -13995,7 +13944,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65"/>
       <c r="D65" s="34" t="str" cm="1">
         <f t="array" ref="D65">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -14006,7 +13955,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66"/>
       <c r="D66" s="34" t="str" cm="1">
         <f t="array" ref="D66">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -14017,7 +13966,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67"/>
       <c r="D67" s="34" t="str" cm="1">
         <f t="array" ref="D67">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -14028,7 +13977,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68"/>
       <c r="D68" s="34" t="str" cm="1">
         <f t="array" ref="D68">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -14039,7 +13988,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69"/>
       <c r="D69" s="34" t="str" cm="1">
         <f t="array" ref="D69">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -14050,7 +13999,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70"/>
       <c r="D70" s="34" t="str" cm="1">
         <f t="array" ref="D70">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -14061,7 +14010,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71"/>
       <c r="D71" s="34" t="str" cm="1">
         <f t="array" ref="D71">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -14072,7 +14021,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72"/>
       <c r="D72" s="34" t="str" cm="1">
         <f t="array" ref="D72">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -14083,7 +14032,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73"/>
       <c r="D73" s="34" t="str" cm="1">
         <f t="array" ref="D73">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -14094,7 +14043,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74"/>
       <c r="D74" s="34" t="str" cm="1">
         <f t="array" ref="D74">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -14105,7 +14054,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75"/>
       <c r="D75" s="34" t="str" cm="1">
         <f t="array" ref="D75">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -14116,7 +14065,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76"/>
       <c r="D76" s="34" t="str" cm="1">
         <f t="array" ref="D76">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -14127,7 +14076,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77"/>
       <c r="D77" s="34" t="str" cm="1">
         <f t="array" ref="D77">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -14138,64 +14087,64 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78"/>
     </row>
-    <row r="79" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79"/>
     </row>
-    <row r="80" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80"/>
     </row>
-    <row r="81" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81"/>
       <c r="D81" s="6" t="str" cm="1">
         <f t="array" ref="D81">Common_SourceData.Common_SourceData_ClimateZones_Title()</f>
         <v>VEERG Australian climate zones</v>
       </c>
     </row>
-    <row r="82" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82"/>
       <c r="D82" s="5" t="str" cm="1">
         <f t="array" ref="D82">Common_SourceData.Common_SourceData_ClimateZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="83" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83"/>
       <c r="D83" s="49" t="str" cm="1">
         <f t="array" ref="D83:D87">"⚠️" &amp; Common_SourceData.Common_SourceData_ClimateZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="84" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84"/>
       <c r="D84" s="49" t="str">
         <v>⚠️Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.</v>
       </c>
     </row>
-    <row r="85" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85"/>
       <c r="D85" s="49" t="str">
         <v>⚠️Fixed typo in MAT value for warm temperate dry - changed 10 to 11.</v>
       </c>
     </row>
-    <row r="86" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86"/>
       <c r="D86" s="49" t="str">
         <v>⚠️Added min and max columns for MAT, MAP, frost days per year, elevation, MAP:PET to calculate zones from real climate data.</v>
       </c>
     </row>
-    <row r="87" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87"/>
       <c r="D87" s="49" t="str">
         <v>⚠️GAF accepts rainfall as a proxy for precipitation.</v>
       </c>
     </row>
-    <row r="88" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88"/>
     </row>
-    <row r="89" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89"/>
       <c r="D89" s="34" t="s">
         <v>5</v>
@@ -14247,7 +14196,7 @@
       </c>
       <c r="T89" s="34"/>
     </row>
-    <row r="90" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90"/>
       <c r="D90" s="34" t="str" cm="1">
         <f t="array" ref="D90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -14315,7 +14264,7 @@
       </c>
       <c r="T90" s="34"/>
     </row>
-    <row r="91" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91"/>
       <c r="D91" s="34" t="str" cm="1">
         <f t="array" ref="D91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -14383,7 +14332,7 @@
       </c>
       <c r="T91" s="34"/>
     </row>
-    <row r="92" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92"/>
       <c r="D92" s="34" t="str" cm="1">
         <f t="array" ref="D92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -14451,7 +14400,7 @@
       </c>
       <c r="T92" s="34"/>
     </row>
-    <row r="93" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93"/>
       <c r="D93" s="34" t="str" cm="1">
         <f t="array" ref="D93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -14519,7 +14468,7 @@
       </c>
       <c r="T93" s="34"/>
     </row>
-    <row r="94" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94"/>
       <c r="D94" s="34" t="str" cm="1">
         <f t="array" ref="D94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -14587,7 +14536,7 @@
       </c>
       <c r="T94" s="34"/>
     </row>
-    <row r="95" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95"/>
       <c r="D95" s="34" t="str" cm="1">
         <f t="array" ref="D95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -14655,7 +14604,7 @@
       </c>
       <c r="T95" s="34"/>
     </row>
-    <row r="96" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96"/>
       <c r="D96" s="34" t="str" cm="1">
         <f t="array" ref="D96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -14723,7 +14672,7 @@
       </c>
       <c r="T96" s="34"/>
     </row>
-    <row r="97" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97"/>
       <c r="D97" s="34" t="str" cm="1">
         <f t="array" ref="D97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -14791,66 +14740,66 @@
       </c>
       <c r="T97" s="34"/>
     </row>
-    <row r="98" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98"/>
     </row>
-    <row r="99" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99"/>
       <c r="D99" s="48" t="str" cm="1">
         <f t="array" ref="D99:D102">Common_SourceData.Common_SourceData_ClimateZones_Appendices()</f>
         <v>Note:</v>
       </c>
     </row>
-    <row r="100" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100"/>
       <c r="D100" s="48" t="str">
         <v>MAT = mean annual temperature</v>
       </c>
     </row>
-    <row r="101" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101"/>
       <c r="D101" s="48" t="str">
         <v>MAP = mean annual precipitation</v>
       </c>
     </row>
-    <row r="102" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102"/>
       <c r="D102" s="48" t="str">
         <v>PET = potential evapotranspiration</v>
       </c>
     </row>
-    <row r="103" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103"/>
       <c r="D103" s="48"/>
     </row>
-    <row r="104" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104"/>
     </row>
-    <row r="105" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105"/>
       <c r="D105" s="6" t="str" cm="1">
         <f t="array" ref="D105">Common_SourceData.Common_SourceData_TemperatureZones_Title()</f>
         <v>VEERG Australian temperature zones</v>
       </c>
     </row>
-    <row r="106" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106"/>
       <c r="D106" s="5" t="str" cm="1">
         <f t="array" ref="D106">Common_SourceData.Common_SourceData_TemperatureZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="107" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107"/>
       <c r="D107" s="49" t="str" cm="1">
         <f t="array" ref="D107">"⚠️" &amp; Common_SourceData.Common_SourceData_TemperatureZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA: Added extra MAT min and MAT max columns to calculate zone from real temperature data.</v>
       </c>
     </row>
-    <row r="108" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108"/>
     </row>
-    <row r="109" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109"/>
       <c r="D109" s="34" t="s">
         <v>39</v>
@@ -14865,7 +14814,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="110" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110"/>
       <c r="D110" s="34" t="str" cm="1">
         <f t="array" ref="D110">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
@@ -14884,7 +14833,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="111" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111"/>
       <c r="D111" s="34" t="str" cm="1">
         <f t="array" ref="D111">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
@@ -14903,7 +14852,7 @@
         <v>25.998999999999999</v>
       </c>
     </row>
-    <row r="112" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112"/>
       <c r="D112" s="34" t="str" cm="1">
         <f t="array" ref="D112">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
@@ -14922,13 +14871,13 @@
         <v>14.999000000000001</v>
       </c>
     </row>
-    <row r="113" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113"/>
     </row>
-    <row r="114" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114"/>
     </row>
-    <row r="115" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115"/>
       <c r="D115" s="6" t="str" cm="1">
         <f t="array" ref="D115">Common_SourceData.Common_SourceData_RainfallZones_Title()</f>
@@ -14936,7 +14885,7 @@
       </c>
       <c r="BN115" s="7"/>
     </row>
-    <row r="116" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116"/>
       <c r="D116" s="5" t="str" cm="1">
         <f t="array" ref="D116">Common_SourceData.Common_SourceData_RainfallZones_Source()</f>
@@ -14944,7 +14893,7 @@
       </c>
       <c r="BN116" s="7"/>
     </row>
-    <row r="117" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117"/>
       <c r="D117" s="49" t="str" cm="1">
         <f t="array" ref="D117">"⚠️" &amp; Common_SourceData.Common_SourceData_RainfallZones_Variation()</f>
@@ -14952,11 +14901,11 @@
       </c>
       <c r="BN117" s="7"/>
     </row>
-    <row r="118" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118"/>
       <c r="BN118" s="7"/>
     </row>
-    <row r="119" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119"/>
       <c r="D119" s="34" t="s">
         <v>42</v>
@@ -14972,7 +14921,7 @@
       </c>
       <c r="BN119" s="7"/>
     </row>
-    <row r="120" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120"/>
       <c r="D120" s="34" t="str" cm="1">
         <f t="array" ref="D120">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
@@ -14992,7 +14941,7 @@
       </c>
       <c r="BN120" s="7"/>
     </row>
-    <row r="121" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121"/>
       <c r="D121" s="34" t="str" cm="1">
         <f t="array" ref="D121">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
@@ -15012,31 +14961,31 @@
       </c>
       <c r="BN121" s="7"/>
     </row>
-    <row r="122" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122"/>
       <c r="BN122" s="7"/>
     </row>
-    <row r="123" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123"/>
     </row>
-    <row r="124" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124"/>
       <c r="D124" s="6" t="str" cm="1">
         <f t="array" ref="D124">Common_SourceData.Common_SourceData_LeachingZones_Title()</f>
         <v>VEERG Australian leaching zones</v>
       </c>
     </row>
-    <row r="125" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125"/>
       <c r="D125" s="5" t="str" cm="1">
         <f t="array" ref="D125">Common_SourceData.Common_SourceData_LeachingZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="126" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126"/>
     </row>
-    <row r="127" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127"/>
       <c r="D127" s="34" t="s">
         <v>44</v>
@@ -15045,7 +14994,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="128" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128"/>
       <c r="D128" s="34" t="str" cm="1">
         <f t="array" ref="D128">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
@@ -15056,7 +15005,7 @@
         <v>Σ(𝑟𝑎𝑖𝑛)&gt;Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦</v>
       </c>
     </row>
-    <row r="129" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129"/>
       <c r="D129" s="34" t="str" cm="1">
         <f t="array" ref="D129">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
@@ -15067,13 +15016,13 @@
         <v>Σ(𝑟𝑎𝑖𝑛)≤Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦</v>
       </c>
     </row>
-    <row r="130" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130"/>
     </row>
-    <row r="131" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131"/>
     </row>
-    <row r="132" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132"/>
       <c r="D132" s="6" t="str" cm="1">
         <f t="array" ref="D132">Common_SourceData.Common_SourceData_FracWET_Title()</f>
@@ -15081,7 +15030,7 @@
       </c>
       <c r="E132" s="21"/>
     </row>
-    <row r="133" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133"/>
       <c r="D133" s="5" t="str" cm="1">
         <f t="array" ref="D133">Common_SourceData.Common_SourceData_FracWET_Source()</f>
@@ -15089,7 +15038,7 @@
       </c>
       <c r="E133" s="21"/>
     </row>
-    <row r="134" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134"/>
       <c r="D134" t="s">
         <v>55</v>
@@ -15098,7 +15047,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="135" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135"/>
       <c r="D135" t="str" cm="1">
         <f t="array" ref="D135">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
@@ -15109,7 +15058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136"/>
       <c r="D136" s="1" t="str" cm="1">
         <f t="array" ref="D136">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
@@ -15120,10 +15069,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137"/>
     </row>
-    <row r="138" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138"/>
       <c r="BN138" s="7"/>
       <c r="BO138" s="7"/>
@@ -15138,7 +15087,7 @@
       <c r="BX138" s="7"/>
       <c r="BY138" s="7"/>
     </row>
-    <row r="139" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139"/>
       <c r="D139" s="6" t="str" cm="1">
         <f t="array" ref="D139">Common_SourceData.Common_SourceData_FracWETIrrigation_Title()</f>
@@ -15157,7 +15106,7 @@
       <c r="BX139" s="7"/>
       <c r="BY139" s="7"/>
     </row>
-    <row r="140" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140"/>
       <c r="D140" s="5" t="str" cm="1">
         <f t="array" ref="D140">Common_SourceData.Common_SourceData_FracWETIrrigation_Source()</f>
@@ -15176,7 +15125,7 @@
       <c r="BX140" s="7"/>
       <c r="BY140" s="7"/>
     </row>
-    <row r="141" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141"/>
       <c r="D141" s="49" t="str" cm="1">
         <f t="array" ref="D141">Common_SourceData.Common_SourceData_FracWETIrrigation_Variation()</f>
@@ -15184,7 +15133,7 @@
       </c>
       <c r="BN141" s="7"/>
     </row>
-    <row r="142" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142"/>
       <c r="D142" s="34" t="s">
         <v>71</v>
@@ -15194,7 +15143,7 @@
       </c>
       <c r="BN142" s="7"/>
     </row>
-    <row r="143" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143"/>
       <c r="D143" s="34" t="str" cm="1">
         <f t="array" ref="D143">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -15206,7 +15155,7 @@
       </c>
       <c r="BN143" s="7"/>
     </row>
-    <row r="144" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144"/>
       <c r="D144" s="1" t="str" cm="1">
         <f t="array" ref="D144">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -15218,7 +15167,7 @@
       </c>
       <c r="BN144" s="7"/>
     </row>
-    <row r="145" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145"/>
       <c r="D145" s="1" t="str" cm="1">
         <f t="array" ref="D145">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -15230,7 +15179,7 @@
       </c>
       <c r="BN145" s="7"/>
     </row>
-    <row r="146" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146"/>
       <c r="D146" s="1" t="str" cm="1">
         <f t="array" ref="D146">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -15242,7 +15191,7 @@
       </c>
       <c r="BN146" s="7"/>
     </row>
-    <row r="147" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147"/>
       <c r="D147" s="1" t="str" cm="1">
         <f t="array" ref="D147">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -15254,15 +15203,15 @@
       </c>
       <c r="BN147" s="7"/>
     </row>
-    <row r="148" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148"/>
       <c r="BN148" s="7"/>
     </row>
-    <row r="149" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149"/>
       <c r="BN149" s="7"/>
     </row>
-    <row r="150" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150"/>
       <c r="D150" s="6" t="str" cm="1">
         <f t="array" ref="D150">Common_SourceData.Common_SourceData_DataScores_Scope3_Title()</f>
@@ -15270,7 +15219,7 @@
       </c>
       <c r="BN150" s="7"/>
     </row>
-    <row r="151" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151"/>
       <c r="D151" s="5" t="str" cm="1">
         <f t="array" ref="D151">Common_SourceData.Common_SourceData_DataScores_Scope3_Source()</f>
@@ -15278,11 +15227,11 @@
       </c>
       <c r="BN151" s="7"/>
     </row>
-    <row r="152" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152"/>
       <c r="BN152" s="7"/>
     </row>
-    <row r="153" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153"/>
       <c r="D153" s="34" t="s">
         <v>46</v>
@@ -15302,7 +15251,7 @@
       <c r="BL153" s="3"/>
       <c r="BM153" s="3"/>
     </row>
-    <row r="154" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154"/>
       <c r="D154" s="34" t="str" cm="1">
         <f t="array" ref="D154">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -15324,7 +15273,7 @@
       <c r="BL154" s="3"/>
       <c r="BM154" s="3"/>
     </row>
-    <row r="155" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155"/>
       <c r="D155" s="34" t="str" cm="1">
         <f t="array" ref="D155">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -15346,7 +15295,7 @@
       <c r="BL155" s="3"/>
       <c r="BM155" s="3"/>
     </row>
-    <row r="156" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156"/>
       <c r="D156" s="34" t="str" cm="1">
         <f t="array" ref="D156">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -15357,7 +15306,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="157" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157"/>
       <c r="D157" s="34" t="str" cm="1">
         <f t="array" ref="D157">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -15368,7 +15317,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="158" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158"/>
       <c r="D158" s="34" t="str" cm="1">
         <f t="array" ref="D158">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -15379,34 +15328,34 @@
         <v>5</v>
       </c>
     </row>
-    <row r="159" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159"/>
     </row>
-    <row r="160" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160"/>
     </row>
-    <row r="161" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D161" s="6" t="str" cm="1">
         <f t="array" ref="D161">Common_SourceData.Common_SourceData_FracLEACH_Title()</f>
         <v>Fraction of N that is available for leaching and runoff</v>
       </c>
       <c r="E161" s="21"/>
     </row>
-    <row r="162" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D162" s="5" t="str" cm="1">
         <f t="array" ref="D162">Common_SourceData.Common_SourceData_FracLEACH_Source()</f>
         <v>VEERG 2026:5.5.2.3 Constant Parameters</v>
       </c>
       <c r="E162" s="21"/>
     </row>
-    <row r="163" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D163" s="5" t="str" cm="1">
         <f t="array" ref="D163">Common_SourceData.Common_SourceData_FracLEACH_NIRReference()</f>
         <v>National Inventory Report Volume 1: Leaching and runoff (3.D.b.2)</v>
       </c>
       <c r="E163" s="21"/>
     </row>
-    <row r="164" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D164" s="21" t="str" cm="1">
         <f t="array" ref="D164:E164">Common_SourceData.Common_SourceData_FracLEACH_Data()</f>
         <v>FracLEACH</v>
@@ -15415,17 +15364,17 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="165" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN165" s="7"/>
       <c r="BO165" s="7"/>
       <c r="BP165" s="7"/>
     </row>
-    <row r="166" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN166" s="7"/>
       <c r="BO166" s="7"/>
       <c r="BP166" s="7"/>
     </row>
-    <row r="167" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D167" s="6" t="str" cm="1">
         <f t="array" ref="D167">Common_SourceData.Common_SourceData_EFleach_Title()</f>
         <v>Emission factor for nitrogen leaching and runoff</v>
@@ -15434,7 +15383,7 @@
       <c r="BO167" s="7"/>
       <c r="BP167" s="7"/>
     </row>
-    <row r="168" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D168" s="5" t="str" cm="1">
         <f t="array" ref="D168">Common_SourceData.Common_SourceData_EFleach_Source()</f>
         <v>VEERG 2026:5.5.2.3 Constant Parameters</v>
@@ -15443,7 +15392,7 @@
       <c r="BO168" s="7"/>
       <c r="BP168" s="7"/>
     </row>
-    <row r="169" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D169" s="5" t="str" cm="1">
         <f t="array" ref="D169">Common_SourceData.Common_SourceData_EFleach_NIRReference()</f>
         <v>National Inventory Report Volume 1: Equation 3.D.B_10</v>
@@ -15452,7 +15401,7 @@
       <c r="BO169" s="7"/>
       <c r="BP169" s="7"/>
     </row>
-    <row r="170" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D170" s="1" t="str" cm="1">
         <f t="array" ref="D170:E170">Common_SourceData.Common_SourceData_EFleach_Data()</f>
         <v>EFleach</v>
@@ -15464,17 +15413,17 @@
       <c r="BO170" s="7"/>
       <c r="BP170" s="7"/>
     </row>
-    <row r="171" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN171" s="7"/>
       <c r="BO171" s="7"/>
       <c r="BP171" s="7"/>
     </row>
-    <row r="172" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN172" s="7"/>
       <c r="BO172" s="7"/>
       <c r="BP172" s="7"/>
     </row>
-    <row r="173" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D173" s="6" t="str" cm="1">
         <f t="array" ref="D173">Common_SourceData.Common_SourceData_DensityOfMethane_Title()</f>
         <v>p = density of methane</v>
@@ -15483,7 +15432,7 @@
       <c r="BO173" s="7"/>
       <c r="BP173" s="7"/>
     </row>
-    <row r="174" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D174" s="5" t="str" cm="1">
         <f t="array" ref="D174">Common_SourceData.Common_SourceData_DensityOfMethane_Source()</f>
         <v>National Inventory Report 2023 Volume 1: Equations 3.B.1a_2, 3.B.1c_2, 3.B.3_1, 3.B.4g_2</v>
@@ -15492,7 +15441,7 @@
       <c r="BO174" s="7"/>
       <c r="BP174" s="7"/>
     </row>
-    <row r="175" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D175" s="1" cm="1">
         <f t="array" ref="D175">Common_SourceData.Common_SourceData_DensityOfMethane_Data()</f>
         <v>0.6784</v>
@@ -15505,17 +15454,17 @@
       <c r="BO175" s="7"/>
       <c r="BP175" s="7"/>
     </row>
-    <row r="176" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN176" s="7"/>
       <c r="BO176" s="7"/>
       <c r="BP176" s="7"/>
     </row>
-    <row r="177" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN177" s="7"/>
       <c r="BO177" s="7"/>
       <c r="BP177" s="7"/>
     </row>
-    <row r="178" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D178" s="6" t="str" cm="1">
         <f t="array" ref="D178">Common_SourceData.Common_SourceData_EFN2O_Title()</f>
         <v>Nitrous oxide emission factors for inorganic fertiliser application</v>
@@ -15524,7 +15473,7 @@
       <c r="BO178" s="7"/>
       <c r="BP178" s="7"/>
     </row>
-    <row r="179" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D179" s="5" t="str" cm="1">
         <f t="array" ref="D179">Common_SourceData.Common_SourceData_EFN2O_Source()</f>
         <v>VEERG 2026: Table A.2.2.1</v>
@@ -15533,39 +15482,39 @@
       <c r="BO179" s="7"/>
       <c r="BP179" s="7"/>
     </row>
-    <row r="180" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D180" s="48" t="str" cm="1">
         <f t="array" ref="D180">Common_SourceData.Common_SourceData_EFN2O_Unit()</f>
         <v>(kg N2O-N / kg N</v>
       </c>
     </row>
-    <row r="181" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D181" s="49" t="str" cm="1">
         <f t="array" ref="D181:D185">Common_SourceData.Common_SourceData_EFN2O_Variation()</f>
         <v>VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="182" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D182" s="49" t="str">
         <v>Removed duplicate 'Aquaculture' row.</v>
       </c>
     </row>
-    <row r="183" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D183" s="49" t="str">
         <v>Removed asterisks to aid lookup.</v>
       </c>
     </row>
-    <row r="184" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D184" s="49" t="str">
         <v>Added 'production system only', 'rainfall zone' and 'irrigation method' columns to aid lookup.</v>
       </c>
     </row>
-    <row r="185" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D185" s="49" t="str">
         <v>Duplicated 'non-irrigated pasture' row with same EF for low and high rainfall zones to aid lookup.</v>
       </c>
     </row>
-    <row r="186" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D186" s="34" t="s">
         <v>63</v>
       </c>
@@ -15582,7 +15531,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="187" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D187" s="34" t="str" cm="1">
         <f t="array" ref="D187">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Irrigated pasture</v>
@@ -15604,7 +15553,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="188" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D188" s="34" t="str" cm="1">
         <f t="array" ref="D188">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Irrigated crop</v>
@@ -15626,7 +15575,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="189" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D189" s="34" t="str" cm="1">
         <f t="array" ref="D189">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated pasture</v>
@@ -15648,7 +15597,7 @@
         <v>Low rainfall</v>
       </c>
     </row>
-    <row r="190" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D190" s="34" t="str" cm="1">
         <f t="array" ref="D190">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated pasture</v>
@@ -15670,7 +15619,7 @@
         <v>High rainfall</v>
       </c>
     </row>
-    <row r="191" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D191" s="34" t="str" cm="1">
         <f t="array" ref="D191">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated crop (low rainfall)</v>
@@ -15692,7 +15641,7 @@
         <v>Low rainfall</v>
       </c>
     </row>
-    <row r="192" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D192" s="34" t="str" cm="1">
         <f t="array" ref="D192">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated crop (high rainfall)</v>
@@ -15714,7 +15663,7 @@
         <v>High rainfall</v>
       </c>
     </row>
-    <row r="193" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D193" s="34" t="str" cm="1">
         <f t="array" ref="D193">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Sugar</v>
@@ -15736,7 +15685,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="194" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D194" s="34" t="str" cm="1">
         <f t="array" ref="D194">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Cotton</v>
@@ -15758,7 +15707,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="195" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D195" s="34" t="str" cm="1">
         <f t="array" ref="D195">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Horticultural crops</v>
@@ -15780,7 +15729,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="196" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D196" s="34" t="str" cm="1">
         <f t="array" ref="D196">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Rice (continuous flooding)</v>
@@ -15802,7 +15751,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="197" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="197" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D197" s="34" t="str" cm="1">
         <f t="array" ref="D197">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Rice (single and multiple drainage, or alternate wetting and drying)</v>
@@ -15824,7 +15773,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="198" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="198" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D198" s="34" t="str" cm="1">
         <f t="array" ref="D198">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Aquaculture</v>
@@ -15846,7 +15795,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="199" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="199" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D199" s="34" t="str" cm="1">
         <f t="array" ref="D199">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Forestry</v>
@@ -15868,31 +15817,31 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="202" spans="4:8" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="202" spans="4:8" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D202" s="6" t="str" cm="1">
         <f t="array" ref="D202">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Title()</f>
         <v>Emission factor for urine and dung deposited on pasture, range or paddock</v>
       </c>
     </row>
-    <row r="203" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="203" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D203" s="5" t="str" cm="1">
         <f t="array" ref="D203">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Source()</f>
         <v>VEERG 2026: Table A.2.2.2</v>
       </c>
     </row>
-    <row r="204" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="204" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D204" s="49" t="str" cm="1">
         <f t="array" ref="D204">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Variation()</f>
         <v>VARIATION FROM SOURCE DATA: Changed 'Dry climate zones' to singular 'Dry climate zone' to aid lookup.</v>
       </c>
     </row>
-    <row r="205" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="205" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D205" s="48" t="str" cm="1">
         <f t="array" ref="D205">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Unit()</f>
         <v>kg N2O - N / kg N</v>
       </c>
     </row>
-    <row r="206" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="206" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D206" s="34" t="s">
         <v>5</v>
       </c>
@@ -15900,7 +15849,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="207" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="207" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D207" s="34" t="str" cm="1">
         <f t="array" ref="D207">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
         <v>Wet climate zone</v>
@@ -15910,7 +15859,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="208" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="208" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D208" s="1" t="str" cm="1">
         <f t="array" ref="D208">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
         <v>Dry climate zone</v>
@@ -15920,13 +15869,13 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="211" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="211" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D211" s="1" t="str" cm="1">
         <f t="array" ref="D211">Common_SourceData.Common_SourceData_MonthsToSeasons_Title()</f>
         <v>Months to Seasons Mapping</v>
       </c>
     </row>
-    <row r="212" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="212" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D212" s="34" t="s">
         <v>70</v>
       </c>
@@ -15934,7 +15883,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="213" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="213" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D213" s="34" t="str" cm="1">
         <f t="array" ref="D213">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>January</v>
@@ -15944,7 +15893,7 @@
         <v>Summer</v>
       </c>
     </row>
-    <row r="214" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="214" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D214" s="1" t="str" cm="1">
         <f t="array" ref="D214">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>February</v>
@@ -15954,7 +15903,7 @@
         <v>Summer</v>
       </c>
     </row>
-    <row r="215" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="215" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D215" s="1" t="str" cm="1">
         <f t="array" ref="D215">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>March</v>
@@ -15964,7 +15913,7 @@
         <v>Autumn</v>
       </c>
     </row>
-    <row r="216" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="216" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D216" s="1" t="str" cm="1">
         <f t="array" ref="D216">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>April</v>
@@ -15974,7 +15923,7 @@
         <v>Autumn</v>
       </c>
     </row>
-    <row r="217" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="217" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D217" s="1" t="str" cm="1">
         <f t="array" ref="D217">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>May</v>
@@ -15984,7 +15933,7 @@
         <v>Autumn</v>
       </c>
     </row>
-    <row r="218" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="218" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D218" s="1" t="str" cm="1">
         <f t="array" ref="D218">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>June</v>
@@ -15994,7 +15943,7 @@
         <v>Winter</v>
       </c>
     </row>
-    <row r="219" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="219" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D219" s="1" t="str" cm="1">
         <f t="array" ref="D219">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>July</v>
@@ -16004,7 +15953,7 @@
         <v>Winter</v>
       </c>
     </row>
-    <row r="220" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="220" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D220" s="1" t="str" cm="1">
         <f t="array" ref="D220">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>August</v>
@@ -16014,7 +15963,7 @@
         <v>Winter</v>
       </c>
     </row>
-    <row r="221" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="221" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D221" s="1" t="str" cm="1">
         <f t="array" ref="D221">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>September</v>
@@ -16024,7 +15973,7 @@
         <v>Spring</v>
       </c>
     </row>
-    <row r="222" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="222" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D222" s="1" t="str" cm="1">
         <f t="array" ref="D222">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>October</v>
@@ -16034,7 +15983,7 @@
         <v>Spring</v>
       </c>
     </row>
-    <row r="223" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="223" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D223" s="1" t="str" cm="1">
         <f t="array" ref="D223">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>November</v>
@@ -16044,7 +15993,7 @@
         <v>Spring</v>
       </c>
     </row>
-    <row r="224" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="224" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D224" s="1" t="str" cm="1">
         <f t="array" ref="D224">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>December</v>
@@ -16054,25 +16003,25 @@
         <v>Summer</v>
       </c>
     </row>
-    <row r="227" spans="4:19" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="227" spans="4:19" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D227" s="6" t="str" cm="1">
         <f t="array" ref="D227">Common_SourceData.Common_SourceData_MCFTemperatureZone_Title()</f>
         <v>Manure Management – Methane conversion factor per temperature zone (fraction) (MCFim)</v>
       </c>
     </row>
-    <row r="228" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="228" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D228" s="5" t="str" cm="1">
         <f t="array" ref="D228">Common_SourceData.Common_SourceData_MCFTemperatureZone_Source()</f>
         <v>VEERG 2026: Table A.1.8.1</v>
       </c>
     </row>
-    <row r="229" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="229" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D229" s="49" t="str" cm="1">
         <f t="array" ref="D229">Common_SourceData.Common_SourceData_MCFTemperatureZone_Variation()</f>
         <v>VARIATION FROM SOURCE: Added row of NIR MMA definitions to aid lookup. Duplicated 'Poultry with and without litter' column with separate NIR definitions to aid lookup. Added 'MAT raw' column to allow lookup of numbers.</v>
       </c>
     </row>
-    <row r="231" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="231" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D231" s="34" t="s">
         <v>38</v>
       </c>
@@ -16122,7 +16071,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="232" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="232" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D232" s="34" t="str" cm="1">
         <f t="array" ref="D232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -16188,7 +16137,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="233" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="233" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D233" s="1" t="str" cm="1">
         <f t="array" ref="D233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -16254,7 +16203,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="234" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="234" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D234" s="1" t="str" cm="1">
         <f t="array" ref="D234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -16320,7 +16269,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="235" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="235" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D235" s="1" t="str" cm="1">
         <f t="array" ref="D235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -16386,7 +16335,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="236" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="236" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D236" s="1" t="str" cm="1">
         <f t="array" ref="D236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -16452,7 +16401,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="237" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="237" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D237" s="1" t="str" cm="1">
         <f t="array" ref="D237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -16518,7 +16467,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="238" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="238" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D238" s="1" t="str" cm="1">
         <f t="array" ref="D238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -16584,7 +16533,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="239" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="239" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D239" s="1" t="str" cm="1">
         <f t="array" ref="D239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -16650,7 +16599,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="240" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="240" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D240" s="1" t="str" cm="1">
         <f t="array" ref="D240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -16716,7 +16665,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="241" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="241" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D241" s="1" t="str" cm="1">
         <f t="array" ref="D241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -16782,7 +16731,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="242" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="242" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D242" s="1" t="str" cm="1">
         <f t="array" ref="D242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -16848,7 +16797,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="243" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="243" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D243" s="1" t="str" cm="1">
         <f t="array" ref="D243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -16914,7 +16863,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="244" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="244" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D244" s="1" t="str" cm="1">
         <f t="array" ref="D244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -16980,7 +16929,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="245" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="245" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D245" s="1" t="str" cm="1">
         <f t="array" ref="D245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -17046,7 +16995,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="246" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="246" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D246" s="1" t="str" cm="1">
         <f t="array" ref="D246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -17112,7 +17061,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="247" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="247" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D247" s="1" t="str" cm="1">
         <f t="array" ref="D247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -17178,7 +17127,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="248" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="248" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D248" s="1" t="str" cm="1">
         <f t="array" ref="D248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Warm</v>
@@ -17244,7 +17193,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="249" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="249" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D249" s="1" t="str" cm="1">
         <f t="array" ref="D249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Warm</v>
@@ -17310,7 +17259,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="250" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="250" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D250" s="1" t="str" cm="1">
         <f t="array" ref="D250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Warm</v>
@@ -17376,31 +17325,31 @@
         <v>28</v>
       </c>
     </row>
-    <row r="253" spans="4:19" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="253" spans="4:19" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D253" s="6" t="str" cm="1">
         <f t="array" ref="D253">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Title()</f>
         <v>Emission factor for organic fertiliser and crop residues returned to the soil</v>
       </c>
     </row>
-    <row r="254" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="254" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D254" s="5" t="str" cm="1">
         <f t="array" ref="D254">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Source()</f>
         <v>VEERG 2026: Table A.2.1.4</v>
       </c>
     </row>
-    <row r="255" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="255" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D255" s="1" t="str" cm="1">
         <f t="array" ref="D255">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Variable()</f>
         <v>EFNi &amp; EFN2Oi</v>
       </c>
     </row>
-    <row r="256" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="256" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D256" s="48" t="str" cm="1">
         <f t="array" ref="D256">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Unit()</f>
         <v>kg N2O - N / kg N</v>
       </c>
     </row>
-    <row r="257" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="257" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D257" s="34" t="s">
         <v>96</v>
       </c>
@@ -17408,7 +17357,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="258" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="258" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D258" s="34" t="str" cm="1">
         <f t="array" ref="D258">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
         <v>Wet climate zone</v>
@@ -17418,7 +17367,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="259" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="259" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D259" s="1" t="str" cm="1">
         <f t="array" ref="D259">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
         <v>Dry climate zone</v>
@@ -17428,17 +17377,17 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="263" spans="4:6" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="263" spans="4:6" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D263" s="6" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="264" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="264" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D264" s="1" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="265" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="265" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D265" s="34" t="s">
         <v>173</v>
       </c>
@@ -17449,7 +17398,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="266" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="266" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D266" s="34" t="s">
         <v>176</v>
       </c>
@@ -17460,7 +17409,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="267" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="267" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D267" s="34" t="s">
         <v>178</v>
       </c>
@@ -17471,7 +17420,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="268" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="268" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D268" s="34" t="s">
         <v>180</v>
       </c>
@@ -17482,7 +17431,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="269" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="269" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D269" s="34" t="s">
         <v>182</v>
       </c>
@@ -17493,7 +17442,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="270" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="270" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D270" s="34" t="s">
         <v>184</v>
       </c>
@@ -17504,12 +17453,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="273" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D273" s="1" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="274" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="274" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D274" s="34" t="s">
         <v>173</v>
       </c>
@@ -17520,7 +17469,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="275" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="275" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D275" s="34" t="s">
         <v>187</v>
       </c>
@@ -17531,7 +17480,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="276" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="276" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D276" s="34" t="s">
         <v>189</v>
       </c>
@@ -17542,7 +17491,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="277" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="277" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D277" s="34" t="s">
         <v>191</v>
       </c>
@@ -17553,7 +17502,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="278" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="278" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D278" s="34" t="s">
         <v>193</v>
       </c>
@@ -17564,7 +17513,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="279" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="279" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D279" s="34" t="s">
         <v>195</v>
       </c>
@@ -17575,12 +17524,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="282" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="282" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D282" s="1" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="283" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="283" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D283" s="34" t="s">
         <v>173</v>
       </c>
@@ -17591,7 +17540,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="284" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="284" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D284" s="34" t="s">
         <v>198</v>
       </c>
@@ -17602,7 +17551,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="285" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="285" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D285" s="34" t="s">
         <v>200</v>
       </c>
@@ -17613,7 +17562,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="286" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="286" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D286" s="34" t="s">
         <v>202</v>
       </c>
@@ -17624,7 +17573,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="287" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="287" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D287" s="34" t="s">
         <v>204</v>
       </c>
@@ -17635,7 +17584,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="288" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="288" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D288" s="34" t="s">
         <v>206</v>
       </c>
@@ -17646,12 +17595,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="291" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="291" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D291" s="1" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="292" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="292" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D292" s="34" t="s">
         <v>173</v>
       </c>
@@ -17662,7 +17611,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="293" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="293" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D293" s="34" t="s">
         <v>209</v>
       </c>
@@ -17673,7 +17622,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="294" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="294" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D294" s="34" t="s">
         <v>211</v>
       </c>
@@ -17684,7 +17633,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="295" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="295" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D295" s="34" t="s">
         <v>213</v>
       </c>
@@ -17695,7 +17644,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="296" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="296" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D296" s="34" t="s">
         <v>215</v>
       </c>
@@ -17706,7 +17655,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="297" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="297" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D297" s="34" t="s">
         <v>217</v>
       </c>
